--- a/HR_analysis_budget.xlsx
+++ b/HR_analysis_budget.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/mariasazykina/Downloads/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F38A2C0-7E14-214C-9ED3-CE250B14C34F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D174DCB-569D-A440-96FF-8F0E13840531}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1380" yWindow="1740" windowWidth="27440" windowHeight="15680" activeTab="2" xr2:uid="{E448132A-2C0B-BB4B-80EF-CDDB13E0FB6D}"/>
+    <workbookView xWindow="1380" yWindow="1680" windowWidth="27440" windowHeight="15680" xr2:uid="{E448132A-2C0B-BB4B-80EF-CDDB13E0FB6D}"/>
   </bookViews>
   <sheets>
     <sheet name="hr_last" sheetId="2" r:id="rId1"/>
@@ -20,6 +20,8 @@
     <sheet name="График" sheetId="5" r:id="rId5"/>
   </sheets>
   <definedNames>
+    <definedName name="_xlchart.v2.0" hidden="1">График!$A$2:$A$6</definedName>
+    <definedName name="_xlchart.v2.1" hidden="1">График!$B$2:$B$6</definedName>
     <definedName name="ExternalData_1" localSheetId="0" hidden="1">hr_last!$A$1:$M$123</definedName>
     <definedName name="ExternalData_1" localSheetId="1" hidden="1">salary_bands!$A$1:$E$35</definedName>
   </definedNames>
@@ -77,7 +79,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1731" uniqueCount="176">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1599" uniqueCount="187">
   <si>
     <t>employee_id</t>
   </si>
@@ -553,58 +555,91 @@
     <t>полный_оклад</t>
   </si>
   <si>
+    <t>разрыв_до_середины</t>
+  </si>
+  <si>
+    <t>Остаток</t>
+  </si>
+  <si>
+    <t>факт_прибавка_мин</t>
+  </si>
+  <si>
+    <t>факт_прибавка_сер</t>
+  </si>
+  <si>
+    <t>итого_прибавка</t>
+  </si>
+  <si>
+    <t>Отдел</t>
+  </si>
+  <si>
+    <t>Лимит</t>
+  </si>
+  <si>
+    <t>Потребность</t>
+  </si>
+  <si>
+    <t>В рамках лимита</t>
+  </si>
+  <si>
+    <t>Итого</t>
+  </si>
+  <si>
+    <t>Инфраструктура — детализация (лимит 100 000)</t>
+  </si>
+  <si>
     <t>ФИО</t>
   </si>
   <si>
-    <t>проф_группа</t>
-  </si>
-  <si>
-    <t>грейд</t>
-  </si>
-  <si>
-    <t>повышение</t>
-  </si>
-  <si>
-    <t>новый_оклад</t>
-  </si>
-  <si>
-    <t>статус</t>
+    <t>Приоритет</t>
+  </si>
+  <si>
+    <t>Нужно</t>
+  </si>
+  <si>
+    <t>Выделено</t>
+  </si>
+  <si>
+    <t>Статус</t>
   </si>
   <si>
     <t>ниже минимума</t>
   </si>
   <si>
-    <t>разрыв_до_середины</t>
-  </si>
-  <si>
     <t>ниже середины</t>
   </si>
   <si>
-    <t>Итого к распределению</t>
-  </si>
-  <si>
-    <t>Бюджет</t>
-  </si>
-  <si>
-    <t>Остаток</t>
-  </si>
-  <si>
-    <t>до минимума</t>
-  </si>
-  <si>
-    <t>до середины</t>
-  </si>
-  <si>
-    <t>Приоритет 1 - ниже минимума (9 чел.)</t>
-  </si>
-  <si>
-    <t>Приоритет 2 - ниже середины (47 чел.)</t>
-  </si>
-  <si>
-    <t>выше середины</t>
-  </si>
-  <si>
-    <t>выше максимума</t>
+    <t>Поднят</t>
+  </si>
+  <si>
+    <t>Частично</t>
+  </si>
+  <si>
+    <t>Перенос</t>
+  </si>
+  <si>
+    <t>нет вилки (grade 12)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Примечание: 3 стажёра Поддержки (grade 12) исключены из анализа - в salary_bands отсутствует вилка для этого грейда. </t>
+  </si>
+  <si>
+    <t>Количество</t>
+  </si>
+  <si>
+    <t>Ниже минимума</t>
+  </si>
+  <si>
+    <t>Ниже середины</t>
+  </si>
+  <si>
+    <t>Выше середины</t>
+  </si>
+  <si>
+    <t>Выше максимума</t>
+  </si>
+  <si>
+    <t>Нет вилки</t>
   </si>
 </sst>
 </file>
@@ -669,24 +704,63 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="3" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="13">
+  <dxfs count="23">
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -696,6 +770,62 @@
           <bgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
     </dxf>
     <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
@@ -780,10 +910,9 @@
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:rPr lang="ru-RU" sz="1400" b="0" i="0" u="none" strike="noStrike" baseline="0"/>
+              <a:rPr lang="ru-RU"/>
               <a:t>Распределение сотрудников по статусу относительно вилки</a:t>
             </a:r>
-            <a:endParaRPr lang="ru-RU"/>
           </a:p>
         </c:rich>
       </c:tx>
@@ -896,35 +1025,38 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Анализ!$W$1:$W$4</c:f>
+              <c:f>График!$A$2:$A$6</c:f>
               <c:strCache>
-                <c:ptCount val="4"/>
+                <c:ptCount val="5"/>
                 <c:pt idx="0">
-                  <c:v>ниже минимума</c:v>
+                  <c:v>Ниже минимума</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>ниже середины</c:v>
+                  <c:v>Ниже середины</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>выше середины</c:v>
+                  <c:v>Выше середины</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>выше максимума</c:v>
+                  <c:v>Выше максимума</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>Нет вилки</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Анализ!$V$1:$V$4</c:f>
+              <c:f>График!$B$2:$B$6</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="4"/>
+                <c:ptCount val="5"/>
                 <c:pt idx="0">
                   <c:v>9</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>55</c:v>
+                  <c:v>47</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>54</c:v>
@@ -932,18 +1064,22 @@
                 <c:pt idx="3">
                   <c:v>4</c:v>
                 </c:pt>
+                <c:pt idx="4">
+                  <c:v>3</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-C060-0F4F-8A47-2EC8DADE9087}"/>
+              <c16:uniqueId val="{00000000-CCD3-624E-8E5C-C55EE3523085}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
         <c:dLbls>
+          <c:dLblPos val="outEnd"/>
           <c:showLegendKey val="0"/>
-          <c:showVal val="0"/>
+          <c:showVal val="1"/>
           <c:showCatName val="0"/>
           <c:showSerName val="0"/>
           <c:showPercent val="0"/>
@@ -951,11 +1087,11 @@
         </c:dLbls>
         <c:gapWidth val="219"/>
         <c:overlap val="-27"/>
-        <c:axId val="711125247"/>
-        <c:axId val="711126959"/>
+        <c:axId val="771560015"/>
+        <c:axId val="771563055"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="711125247"/>
+        <c:axId val="771560015"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -998,7 +1134,7 @@
             <a:endParaRPr lang="ru-RU"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="711126959"/>
+        <c:crossAx val="771563055"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -1006,7 +1142,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="711126959"/>
+        <c:axId val="771563055"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1057,7 +1193,7 @@
             <a:endParaRPr lang="ru-RU"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="711125247"/>
+        <c:crossAx val="771560015"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -1653,29 +1789,27 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>95250</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>44450</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>12700</xdr:colOff>
-      <xdr:row>15</xdr:row>
-      <xdr:rowOff>63500</xdr:rowOff>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>539750</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>146050</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
         <xdr:cNvPr id="2" name="Диаграмма 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EDF82D78-0F8E-DA4C-8E56-098556A2158E}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4ABE4360-A4FD-88AD-1269-3DB8DBE82516}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
-        <xdr:cNvGraphicFramePr>
-          <a:graphicFrameLocks/>
-        </xdr:cNvGraphicFramePr>
+        <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
         <a:off x="0" y="0"/>
@@ -1733,17 +1867,17 @@
   <autoFilter ref="A1:M123" xr:uid="{AEEAABF5-FDD6-7141-BB0D-0EC755B0537B}"/>
   <tableColumns count="13">
     <tableColumn id="1" xr3:uid="{089B4CC5-73F0-BC4B-AF48-86E203C10F11}" uniqueName="1" name="employee_id" queryTableFieldId="1"/>
-    <tableColumn id="2" xr3:uid="{F7F15DC1-216C-E24B-8CCC-54882DA6030D}" uniqueName="2" name="month" queryTableFieldId="2" dataDxfId="12"/>
-    <tableColumn id="3" xr3:uid="{5AAEE83C-00CF-5E40-9B00-FAB5E2B02E05}" uniqueName="3" name="full_name" queryTableFieldId="3" dataDxfId="11"/>
-    <tableColumn id="4" xr3:uid="{2C9CB250-7F43-E942-B24F-554B78DCDF98}" uniqueName="4" name="dept_l1" queryTableFieldId="4" dataDxfId="10"/>
-    <tableColumn id="5" xr3:uid="{79A765DC-85E6-5048-8BC3-EFCA26D3D36D}" uniqueName="5" name="dept_l2" queryTableFieldId="5" dataDxfId="9"/>
-    <tableColumn id="6" xr3:uid="{36E057D6-B200-A84C-AF2E-8FCAE97A29B8}" uniqueName="6" name="dept_l3" queryTableFieldId="6" dataDxfId="8"/>
-    <tableColumn id="7" xr3:uid="{4D83C4D6-A04F-9141-80F6-BB540B421FDE}" uniqueName="7" name="prof_group" queryTableFieldId="7" dataDxfId="7"/>
-    <tableColumn id="8" xr3:uid="{33DD6341-F95E-7945-9BE1-2C59BB859236}" uniqueName="8" name="role" queryTableFieldId="8" dataDxfId="6"/>
+    <tableColumn id="2" xr3:uid="{F7F15DC1-216C-E24B-8CCC-54882DA6030D}" uniqueName="2" name="month" queryTableFieldId="2" dataDxfId="22"/>
+    <tableColumn id="3" xr3:uid="{5AAEE83C-00CF-5E40-9B00-FAB5E2B02E05}" uniqueName="3" name="full_name" queryTableFieldId="3" dataDxfId="21"/>
+    <tableColumn id="4" xr3:uid="{2C9CB250-7F43-E942-B24F-554B78DCDF98}" uniqueName="4" name="dept_l1" queryTableFieldId="4" dataDxfId="20"/>
+    <tableColumn id="5" xr3:uid="{79A765DC-85E6-5048-8BC3-EFCA26D3D36D}" uniqueName="5" name="dept_l2" queryTableFieldId="5" dataDxfId="19"/>
+    <tableColumn id="6" xr3:uid="{36E057D6-B200-A84C-AF2E-8FCAE97A29B8}" uniqueName="6" name="dept_l3" queryTableFieldId="6" dataDxfId="18"/>
+    <tableColumn id="7" xr3:uid="{4D83C4D6-A04F-9141-80F6-BB540B421FDE}" uniqueName="7" name="prof_group" queryTableFieldId="7" dataDxfId="17"/>
+    <tableColumn id="8" xr3:uid="{33DD6341-F95E-7945-9BE1-2C59BB859236}" uniqueName="8" name="role" queryTableFieldId="8" dataDxfId="16"/>
     <tableColumn id="9" xr3:uid="{39B2188B-CD35-3745-8273-6E1B880FDFE4}" uniqueName="9" name="grade" queryTableFieldId="9"/>
     <tableColumn id="10" xr3:uid="{9F57FC01-EAE6-A647-93BE-42F139576B7D}" uniqueName="10" name="rate" queryTableFieldId="10"/>
     <tableColumn id="11" xr3:uid="{CA916F89-1ED6-FB49-88FE-2EEBB1CC4F47}" uniqueName="11" name="salary" queryTableFieldId="11"/>
-    <tableColumn id="12" xr3:uid="{B6BD8B2B-2509-AA48-A380-5B395F6FF175}" uniqueName="12" name="hire_date" queryTableFieldId="12" dataDxfId="5"/>
+    <tableColumn id="12" xr3:uid="{B6BD8B2B-2509-AA48-A380-5B395F6FF175}" uniqueName="12" name="hire_date" queryTableFieldId="12" dataDxfId="15"/>
     <tableColumn id="13" xr3:uid="{D25CEAF5-C5FB-C145-AAFF-93CCB9759D07}" uniqueName="13" name="manager_id" queryTableFieldId="13"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium7" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -1754,7 +1888,7 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{B7A8102D-87A8-C546-9A3F-B82223B9C458}" name="salary_bands" displayName="salary_bands" ref="A1:E35" tableType="queryTable" totalsRowShown="0">
   <autoFilter ref="A1:E35" xr:uid="{B7A8102D-87A8-C546-9A3F-B82223B9C458}"/>
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{B1739D4F-CD07-DF42-BDA6-60253F565D15}" uniqueName="1" name="prof_group" queryTableFieldId="1" dataDxfId="4"/>
+    <tableColumn id="1" xr3:uid="{B1739D4F-CD07-DF42-BDA6-60253F565D15}" uniqueName="1" name="prof_group" queryTableFieldId="1" dataDxfId="14"/>
     <tableColumn id="2" xr3:uid="{357D2167-D2AD-D643-91BD-4E3586670881}" uniqueName="2" name="grade" queryTableFieldId="2"/>
     <tableColumn id="3" xr3:uid="{AAD57988-2BFD-464C-9DDB-A3D695E9F13C}" uniqueName="3" name="salary_min" queryTableFieldId="3"/>
     <tableColumn id="4" xr3:uid="{9221FA83-F007-D34D-9824-0F6BF4786883}" uniqueName="4" name="salary_mid" queryTableFieldId="4"/>
@@ -1765,11 +1899,11 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{C432BC13-C118-5648-9AEB-5740BCCFA7E6}" name="Таблица3" displayName="Таблица3" ref="A1:T123" totalsRowShown="0">
-  <autoFilter ref="A1:T123" xr:uid="{C432BC13-C118-5648-9AEB-5740BCCFA7E6}"/>
-  <tableColumns count="20">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{C432BC13-C118-5648-9AEB-5740BCCFA7E6}" name="Таблица3" displayName="Таблица3" ref="A1:W123" totalsRowShown="0">
+  <autoFilter ref="A1:W123" xr:uid="{C432BC13-C118-5648-9AEB-5740BCCFA7E6}"/>
+  <tableColumns count="23">
     <tableColumn id="1" xr3:uid="{D238CA7C-9F2D-B841-84EE-256EFA34C1E6}" name="employee_id"/>
-    <tableColumn id="2" xr3:uid="{0A0865B4-57AE-6344-A39A-AB1159A3127C}" name="month" dataDxfId="3"/>
+    <tableColumn id="2" xr3:uid="{0A0865B4-57AE-6344-A39A-AB1159A3127C}" name="month" dataDxfId="13"/>
     <tableColumn id="3" xr3:uid="{FB51149B-C313-264C-BD20-2AAD83DFB3F3}" name="full_name"/>
     <tableColumn id="4" xr3:uid="{EBB1ACA4-79C2-B84C-978E-F798AD6DBE79}" name="dept_l1"/>
     <tableColumn id="5" xr3:uid="{81D45F89-D0F9-494E-8A10-61D591466EEA}" name="dept_l2"/>
@@ -1779,7 +1913,7 @@
     <tableColumn id="9" xr3:uid="{46FB7BBB-9ADA-CD48-87CC-5ADC39FE3C54}" name="grade"/>
     <tableColumn id="10" xr3:uid="{7ECC8D9A-47A4-1849-B8A3-E0EA8EA84948}" name="rate"/>
     <tableColumn id="11" xr3:uid="{28184951-E3E2-6842-A1F3-C28C025A3F16}" name="salary"/>
-    <tableColumn id="12" xr3:uid="{68DD9093-AC87-4747-9445-BB0C4C00AFF0}" name="hire_date" dataDxfId="2"/>
+    <tableColumn id="12" xr3:uid="{68DD9093-AC87-4747-9445-BB0C4C00AFF0}" name="hire_date" dataDxfId="12"/>
     <tableColumn id="13" xr3:uid="{519E4B5E-FBB4-5542-B407-E007B7010B83}" name="manager_id"/>
     <tableColumn id="14" xr3:uid="{E1618BA7-AEC6-AE4A-BA50-13F567C58031}" name="salary_min">
       <calculatedColumnFormula>SUMIFS(salary_bands[salary_min],salary_bands[prof_group],G2,salary_bands[grade],I2)</calculatedColumnFormula>
@@ -1799,8 +1933,17 @@
     <tableColumn id="19" xr3:uid="{C8673600-EDAB-1E45-AAF6-2E2F512E8759}" name="полный_оклад">
       <calculatedColumnFormula>K2/J2</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="20" xr3:uid="{D4501C2F-0342-6F4B-8371-23AA09B1C5C6}" name="разрыв_до_середины" dataDxfId="1">
+    <tableColumn id="20" xr3:uid="{D4501C2F-0342-6F4B-8371-23AA09B1C5C6}" name="разрыв_до_середины" dataDxfId="11">
       <calculatedColumnFormula>IF(S2&lt;O2,O2-S2,0)</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="21" xr3:uid="{CBC7D102-2F01-DA4A-BB6B-46D74401BAC4}" name="факт_прибавка_мин">
+      <calculatedColumnFormula>IF(R2&gt;0, R2*J2, 0)</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="22" xr3:uid="{35F2083A-7655-2D49-9B90-16D61FA46AFF}" name="факт_прибавка_сер" dataDxfId="10">
+      <calculatedColumnFormula>IF(AND(R2=0, T2&gt;3000), T2*J2, 0)</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="23" xr3:uid="{8646BBA3-F155-6F49-9283-D32251EC6AD2}" name="итого_прибавка" dataDxfId="9">
+      <calculatedColumnFormula>U2+V2</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -7461,7 +7604,9 @@
     <col min="18" max="18" width="22.83203125" customWidth="1"/>
     <col min="19" max="19" width="16" customWidth="1"/>
     <col min="20" max="20" width="19.33203125" customWidth="1"/>
-    <col min="23" max="23" width="14.5" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="21.33203125" customWidth="1"/>
+    <col min="22" max="22" width="21" customWidth="1"/>
+    <col min="23" max="23" width="17.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:28" x14ac:dyDescent="0.2">
@@ -7523,14 +7668,16 @@
         <v>157</v>
       </c>
       <c r="T1" t="s">
-        <v>165</v>
-      </c>
-      <c r="V1">
-        <f>COUNTIF(Q2:Q123,"ниже минимума")</f>
-        <v>9</v>
-      </c>
-      <c r="W1" s="9" t="s">
-        <v>164</v>
+        <v>158</v>
+      </c>
+      <c r="U1" t="s">
+        <v>160</v>
+      </c>
+      <c r="V1" t="s">
+        <v>161</v>
+      </c>
+      <c r="W1" t="s">
+        <v>162</v>
       </c>
     </row>
     <row r="2" spans="1:28" x14ac:dyDescent="0.2">
@@ -7598,12 +7745,17 @@
         <f t="shared" ref="T2:T33" si="0">IF(S2&lt;O2,O2-S2,0)</f>
         <v>15000</v>
       </c>
+      <c r="U2">
+        <f>IF(R2&gt;0, R2*J2, 0)</f>
+        <v>0</v>
+      </c>
       <c r="V2">
-        <f>COUNTIF(Q2:Q123,"ниже середины")</f>
-        <v>55</v>
-      </c>
-      <c r="W2" s="9" t="s">
-        <v>166</v>
+        <f t="shared" ref="V2:V33" si="1">IF(AND(R2=0, T2&gt;3000), T2*J2, 0)</f>
+        <v>7500</v>
+      </c>
+      <c r="W2" s="4">
+        <f t="shared" ref="W2:W32" si="2">U2+V2</f>
+        <v>7500</v>
       </c>
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
@@ -7660,23 +7812,28 @@
         <v>ниже середины</v>
       </c>
       <c r="R3">
-        <f t="shared" ref="R3:R66" si="1">IF(S3&lt;N3,N3-S3,0)</f>
+        <f t="shared" ref="R3:R66" si="3">IF(S3&lt;N3,N3-S3,0)</f>
         <v>0</v>
       </c>
       <c r="S3">
-        <f t="shared" ref="S3:S66" si="2">K3/J3</f>
+        <f t="shared" ref="S3:S66" si="4">K3/J3</f>
         <v>165000</v>
       </c>
       <c r="T3">
         <f t="shared" si="0"/>
         <v>15000</v>
       </c>
+      <c r="U3">
+        <f t="shared" ref="U3:U66" si="5">IF(R3&gt;0, R3*J3, 0)</f>
+        <v>0</v>
+      </c>
       <c r="V3">
-        <f>COUNTIF(Q2:Q123,"выше середины")</f>
-        <v>54</v>
-      </c>
-      <c r="W3" s="9" t="s">
-        <v>174</v>
+        <f t="shared" si="1"/>
+        <v>15000</v>
+      </c>
+      <c r="W3" s="4">
+        <f t="shared" si="2"/>
+        <v>15000</v>
       </c>
     </row>
     <row r="4" spans="1:28" x14ac:dyDescent="0.2">
@@ -7733,23 +7890,28 @@
         <v>выше середины</v>
       </c>
       <c r="R4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="S4">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>207000</v>
       </c>
       <c r="T4">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
+      <c r="U4">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
       <c r="V4">
-        <f>COUNTIF(Q2:Q123,"выше максимума")</f>
-        <v>4</v>
-      </c>
-      <c r="W4" s="9" t="s">
-        <v>175</v>
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="W4" s="4">
+        <f t="shared" si="2"/>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:28" x14ac:dyDescent="0.2">
@@ -7806,18 +7968,30 @@
         <v>ниже середины</v>
       </c>
       <c r="R5">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="S5">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>174000</v>
       </c>
       <c r="T5">
         <f t="shared" si="0"/>
         <v>16000</v>
       </c>
-      <c r="AB5" s="9"/>
+      <c r="U5">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V5">
+        <f t="shared" si="1"/>
+        <v>16000</v>
+      </c>
+      <c r="W5">
+        <f t="shared" si="2"/>
+        <v>16000</v>
+      </c>
+      <c r="AB5" s="4"/>
     </row>
     <row r="6" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A6">
@@ -7873,18 +8047,30 @@
         <v>ниже середины</v>
       </c>
       <c r="R6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="S6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>209000</v>
       </c>
       <c r="T6">
         <f t="shared" si="0"/>
         <v>1000</v>
       </c>
-      <c r="AB6" s="9"/>
+      <c r="U6">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="W6">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AB6" s="4"/>
     </row>
     <row r="7" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A7">
@@ -7940,18 +8126,30 @@
         <v>ниже середины</v>
       </c>
       <c r="R7">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="S7">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>188000</v>
       </c>
       <c r="T7">
         <f t="shared" si="0"/>
         <v>12000</v>
       </c>
-      <c r="AB7" s="9"/>
+      <c r="U7">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V7">
+        <f t="shared" si="1"/>
+        <v>12000</v>
+      </c>
+      <c r="W7">
+        <f t="shared" si="2"/>
+        <v>12000</v>
+      </c>
+      <c r="AB7" s="4"/>
     </row>
     <row r="8" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A8">
@@ -8007,18 +8205,30 @@
         <v>выше середины</v>
       </c>
       <c r="R8">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="S8">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>216000</v>
       </c>
       <c r="T8">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="AB8" s="9"/>
+      <c r="U8">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V8">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="W8">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AB8" s="4"/>
     </row>
     <row r="9" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A9">
@@ -8074,15 +8284,27 @@
         <v>выше середины</v>
       </c>
       <c r="R9">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="S9">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>231000</v>
       </c>
       <c r="T9">
         <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U9">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V9">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="W9">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
@@ -8140,15 +8362,27 @@
         <v>выше середины</v>
       </c>
       <c r="R10">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="S10">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>222000</v>
       </c>
       <c r="T10">
         <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U10">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="W10">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
@@ -8206,17 +8440,29 @@
         <v>ниже середины</v>
       </c>
       <c r="R11">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="S11">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>195000</v>
       </c>
       <c r="T11">
         <f t="shared" si="0"/>
         <v>15000</v>
       </c>
+      <c r="U11">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V11">
+        <f t="shared" si="1"/>
+        <v>15000</v>
+      </c>
+      <c r="W11">
+        <f t="shared" si="2"/>
+        <v>15000</v>
+      </c>
     </row>
     <row r="12" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A12">
@@ -8272,17 +8518,29 @@
         <v>ниже середины</v>
       </c>
       <c r="R12">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="S12">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>203000</v>
       </c>
       <c r="T12">
         <f t="shared" si="0"/>
         <v>7000</v>
       </c>
+      <c r="U12">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V12">
+        <f t="shared" si="1"/>
+        <v>4200</v>
+      </c>
+      <c r="W12">
+        <f t="shared" si="2"/>
+        <v>4200</v>
+      </c>
     </row>
     <row r="13" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A13">
@@ -8338,15 +8596,27 @@
         <v>выше середины</v>
       </c>
       <c r="R13">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="S13">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>247000</v>
       </c>
       <c r="T13">
         <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U13">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V13">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="W13">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
@@ -8404,15 +8674,27 @@
         <v>выше середины</v>
       </c>
       <c r="R14">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="S14">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>224000</v>
       </c>
       <c r="T14">
         <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U14">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V14">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="W14">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
@@ -8470,15 +8752,27 @@
         <v>выше середины</v>
       </c>
       <c r="R15">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="S15">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>253000</v>
       </c>
       <c r="T15">
         <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U15">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V15">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="W15">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
@@ -8536,19 +8830,31 @@
         <v>выше середины</v>
       </c>
       <c r="R16">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="S16">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>250000</v>
       </c>
       <c r="T16">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="17" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U16">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V16">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="W16">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A17">
         <v>1015</v>
       </c>
@@ -8602,19 +8908,31 @@
         <v>ниже середины</v>
       </c>
       <c r="R17">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="S17">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>228000</v>
       </c>
       <c r="T17">
         <f t="shared" si="0"/>
         <v>2000</v>
       </c>
-    </row>
-    <row r="18" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U17">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V17">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="W17">
+        <f>U17+V17</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A18">
         <v>1016</v>
       </c>
@@ -8668,19 +8986,31 @@
         <v>ниже середины</v>
       </c>
       <c r="R18">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="S18">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>163000</v>
       </c>
       <c r="T18">
         <f t="shared" si="0"/>
         <v>3000</v>
       </c>
-    </row>
-    <row r="19" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U18">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V18">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="W18">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A19">
         <v>1017</v>
       </c>
@@ -8734,19 +9064,31 @@
         <v>ниже середины</v>
       </c>
       <c r="R19">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="S19">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>146000</v>
       </c>
       <c r="T19">
         <f t="shared" si="0"/>
         <v>20000</v>
       </c>
-    </row>
-    <row r="20" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U19">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V19">
+        <f t="shared" si="1"/>
+        <v>20000</v>
+      </c>
+      <c r="W19">
+        <f t="shared" si="2"/>
+        <v>20000</v>
+      </c>
+    </row>
+    <row r="20" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A20">
         <v>1018</v>
       </c>
@@ -8800,19 +9142,31 @@
         <v>выше середины</v>
       </c>
       <c r="R20">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="S20">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>189000</v>
       </c>
       <c r="T20">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U20">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V20">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="W20">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A21">
         <v>1019</v>
       </c>
@@ -8866,19 +9220,31 @@
         <v>ниже середины</v>
       </c>
       <c r="R21">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="S21">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>161000</v>
       </c>
       <c r="T21">
         <f t="shared" si="0"/>
         <v>14000</v>
       </c>
-    </row>
-    <row r="22" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U21">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V21">
+        <f t="shared" si="1"/>
+        <v>8400</v>
+      </c>
+      <c r="W21">
+        <f t="shared" si="2"/>
+        <v>8400</v>
+      </c>
+    </row>
+    <row r="22" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A22">
         <v>1020</v>
       </c>
@@ -8932,19 +9298,31 @@
         <v>выше середины</v>
       </c>
       <c r="R22">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="S22">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>189000</v>
       </c>
       <c r="T22">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U22">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V22">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="W22">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A23">
         <v>1021</v>
       </c>
@@ -8998,19 +9376,31 @@
         <v>выше середины</v>
       </c>
       <c r="R23">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="S23">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>198000</v>
       </c>
       <c r="T23">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="24" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U23">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V23">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="W23">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A24">
         <v>1022</v>
       </c>
@@ -9064,19 +9454,31 @@
         <v>выше середины</v>
       </c>
       <c r="R24">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="S24">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>185000</v>
       </c>
       <c r="T24">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U24">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V24">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="W24">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A25">
         <v>1023</v>
       </c>
@@ -9130,19 +9532,31 @@
         <v>выше середины</v>
       </c>
       <c r="R25">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="S25">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>189000</v>
       </c>
       <c r="T25">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U25">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V25">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="W25">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A26">
         <v>1024</v>
       </c>
@@ -9196,19 +9610,31 @@
         <v>выше середины</v>
       </c>
       <c r="R26">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="S26">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>217000</v>
       </c>
       <c r="T26">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="27" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U26">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V26">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="W26">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A27">
         <v>1025</v>
       </c>
@@ -9262,19 +9688,31 @@
         <v>ниже середины</v>
       </c>
       <c r="R27">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="S27">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>176000</v>
       </c>
       <c r="T27">
         <f t="shared" si="0"/>
         <v>17000</v>
       </c>
-    </row>
-    <row r="28" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U27">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V27">
+        <f t="shared" si="1"/>
+        <v>17000</v>
+      </c>
+      <c r="W27">
+        <f t="shared" si="2"/>
+        <v>17000</v>
+      </c>
+    </row>
+    <row r="28" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A28">
         <v>1026</v>
       </c>
@@ -9328,19 +9766,31 @@
         <v>ниже середины</v>
       </c>
       <c r="R28">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="S28">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>178000</v>
       </c>
       <c r="T28">
         <f t="shared" si="0"/>
         <v>24000</v>
       </c>
-    </row>
-    <row r="29" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U28">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V28">
+        <f t="shared" si="1"/>
+        <v>24000</v>
+      </c>
+      <c r="W28">
+        <f t="shared" si="2"/>
+        <v>24000</v>
+      </c>
+    </row>
+    <row r="29" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A29">
         <v>1027</v>
       </c>
@@ -9394,19 +9844,31 @@
         <v>выше середины</v>
       </c>
       <c r="R29">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="S29">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>216000</v>
       </c>
       <c r="T29">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U29">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V29">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="W29">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A30">
         <v>1028</v>
       </c>
@@ -9460,19 +9922,31 @@
         <v>ниже середины</v>
       </c>
       <c r="R30">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="S30">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>187000</v>
       </c>
       <c r="T30">
         <f t="shared" si="0"/>
         <v>15000</v>
       </c>
-    </row>
-    <row r="31" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U30">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V30">
+        <f t="shared" si="1"/>
+        <v>4500</v>
+      </c>
+      <c r="W30">
+        <f t="shared" si="2"/>
+        <v>4500</v>
+      </c>
+    </row>
+    <row r="31" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A31">
         <v>1029</v>
       </c>
@@ -9526,19 +10000,31 @@
         <v>ниже середины</v>
       </c>
       <c r="R31">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="S31">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>200000</v>
       </c>
       <c r="T31">
         <f t="shared" si="0"/>
         <v>2000</v>
       </c>
-    </row>
-    <row r="32" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U31">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V31">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="W31">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A32">
         <v>1030</v>
       </c>
@@ -9592,19 +10078,31 @@
         <v>ниже середины</v>
       </c>
       <c r="R32">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="S32">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>142000</v>
       </c>
       <c r="T32">
         <f t="shared" si="0"/>
         <v>16000</v>
       </c>
-    </row>
-    <row r="33" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U32">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V32">
+        <f t="shared" si="1"/>
+        <v>8000</v>
+      </c>
+      <c r="W32">
+        <f t="shared" si="2"/>
+        <v>8000</v>
+      </c>
+    </row>
+    <row r="33" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A33">
         <v>1031</v>
       </c>
@@ -9658,19 +10156,31 @@
         <v>ниже середины</v>
       </c>
       <c r="R33">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="S33">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>152000</v>
       </c>
       <c r="T33">
         <f t="shared" si="0"/>
         <v>6000</v>
       </c>
-    </row>
-    <row r="34" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U33">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V33">
+        <f t="shared" si="1"/>
+        <v>3000</v>
+      </c>
+      <c r="W33">
+        <f>U33+V33</f>
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="34" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A34">
         <v>1032</v>
       </c>
@@ -9724,19 +10234,31 @@
         <v>выше середины</v>
       </c>
       <c r="R34">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="S34">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>179000</v>
       </c>
       <c r="T34">
-        <f t="shared" ref="T34:T65" si="3">IF(S34&lt;O34,O34-S34,0)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="35" spans="1:20" x14ac:dyDescent="0.2">
+        <f t="shared" ref="T34:T65" si="6">IF(S34&lt;O34,O34-S34,0)</f>
+        <v>0</v>
+      </c>
+      <c r="U34">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V34">
+        <f t="shared" ref="V34:V65" si="7">IF(AND(R34=0, T34&gt;3000), T34*J34, 0)</f>
+        <v>0</v>
+      </c>
+      <c r="W34">
+        <f t="shared" ref="W34:W65" si="8">U34+V34</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A35">
         <v>1033</v>
       </c>
@@ -9790,19 +10312,31 @@
         <v>ниже середины</v>
       </c>
       <c r="R35">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="S35">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>145000</v>
       </c>
       <c r="T35">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>22000</v>
       </c>
-    </row>
-    <row r="36" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U35">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V35">
+        <f t="shared" si="7"/>
+        <v>22000</v>
+      </c>
+      <c r="W35">
+        <f t="shared" si="8"/>
+        <v>22000</v>
+      </c>
+    </row>
+    <row r="36" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A36">
         <v>1034</v>
       </c>
@@ -9856,19 +10390,31 @@
         <v>ниже середины</v>
       </c>
       <c r="R36">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="S36">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>167000</v>
       </c>
       <c r="T36">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="37" spans="1:20" x14ac:dyDescent="0.2">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="U36">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V36">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="W36">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A37">
         <v>1035</v>
       </c>
@@ -9922,19 +10468,31 @@
         <v>выше середины</v>
       </c>
       <c r="R37">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="S37">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>185000</v>
       </c>
       <c r="T37">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="38" spans="1:20" x14ac:dyDescent="0.2">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="U37">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V37">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="W37">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A38">
         <v>1036</v>
       </c>
@@ -9988,19 +10546,31 @@
         <v>ниже середины</v>
       </c>
       <c r="R38">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="S38">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>152000</v>
       </c>
       <c r="T38">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>24000</v>
       </c>
-    </row>
-    <row r="39" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U38">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V38">
+        <f t="shared" si="7"/>
+        <v>24000</v>
+      </c>
+      <c r="W38">
+        <f t="shared" si="8"/>
+        <v>24000</v>
+      </c>
+    </row>
+    <row r="39" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A39">
         <v>1037</v>
       </c>
@@ -10054,19 +10624,31 @@
         <v>выше середины</v>
       </c>
       <c r="R39">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="S39">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>187000</v>
       </c>
       <c r="T39">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="40" spans="1:20" x14ac:dyDescent="0.2">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="U39">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V39">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="W39">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A40">
         <v>1038</v>
       </c>
@@ -10120,19 +10702,31 @@
         <v>выше середины</v>
       </c>
       <c r="R40">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="S40">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>209000</v>
       </c>
       <c r="T40">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="41" spans="1:20" x14ac:dyDescent="0.2">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="U40">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V40">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="W40">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A41">
         <v>1039</v>
       </c>
@@ -10186,19 +10780,31 @@
         <v>ниже середины</v>
       </c>
       <c r="R41">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="S41">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>169000</v>
       </c>
       <c r="T41">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>16000</v>
       </c>
-    </row>
-    <row r="42" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U41">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V41">
+        <f t="shared" si="7"/>
+        <v>16000</v>
+      </c>
+      <c r="W41">
+        <f t="shared" si="8"/>
+        <v>16000</v>
+      </c>
+    </row>
+    <row r="42" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A42">
         <v>1040</v>
       </c>
@@ -10252,19 +10858,31 @@
         <v>ниже середины</v>
       </c>
       <c r="R42">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="S42">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>173000</v>
       </c>
       <c r="T42">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>12000</v>
       </c>
-    </row>
-    <row r="43" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U42">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V42">
+        <f t="shared" si="7"/>
+        <v>7200</v>
+      </c>
+      <c r="W42">
+        <f t="shared" si="8"/>
+        <v>7200</v>
+      </c>
+    </row>
+    <row r="43" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A43">
         <v>1041</v>
       </c>
@@ -10318,19 +10936,31 @@
         <v>ниже середины</v>
       </c>
       <c r="R43">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="S43">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>180000</v>
       </c>
       <c r="T43">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>14000</v>
       </c>
-    </row>
-    <row r="44" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U43">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V43">
+        <f t="shared" si="7"/>
+        <v>7000</v>
+      </c>
+      <c r="W43">
+        <f t="shared" si="8"/>
+        <v>7000</v>
+      </c>
+    </row>
+    <row r="44" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A44">
         <v>1042</v>
       </c>
@@ -10384,19 +11014,31 @@
         <v>выше середины</v>
       </c>
       <c r="R44">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="S44">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>207000</v>
       </c>
       <c r="T44">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="45" spans="1:20" x14ac:dyDescent="0.2">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="U44">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V44">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="W44">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A45">
         <v>1043</v>
       </c>
@@ -10450,19 +11092,31 @@
         <v>ниже середины</v>
       </c>
       <c r="R45">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="S45">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>170000</v>
       </c>
       <c r="T45">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>24000</v>
       </c>
-    </row>
-    <row r="46" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U45">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V45">
+        <f t="shared" si="7"/>
+        <v>7200</v>
+      </c>
+      <c r="W45">
+        <f t="shared" si="8"/>
+        <v>7200</v>
+      </c>
+    </row>
+    <row r="46" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A46">
         <v>1044</v>
       </c>
@@ -10516,19 +11170,31 @@
         <v>ниже середины</v>
       </c>
       <c r="R46">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="S46">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>182000</v>
       </c>
       <c r="T46">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>20000</v>
       </c>
-    </row>
-    <row r="47" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U46">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V46">
+        <f t="shared" si="7"/>
+        <v>12000</v>
+      </c>
+      <c r="W46">
+        <f t="shared" si="8"/>
+        <v>12000</v>
+      </c>
+    </row>
+    <row r="47" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A47">
         <v>1045</v>
       </c>
@@ -10582,19 +11248,31 @@
         <v>выше середины</v>
       </c>
       <c r="R47">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="S47">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>225000</v>
       </c>
       <c r="T47">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="48" spans="1:20" x14ac:dyDescent="0.2">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="U47">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V47">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="W47">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A48">
         <v>1046</v>
       </c>
@@ -10648,19 +11326,31 @@
         <v>ниже середины</v>
       </c>
       <c r="R48">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="S48">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>142000</v>
       </c>
       <c r="T48">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>9000</v>
       </c>
-    </row>
-    <row r="49" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U48">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V48">
+        <f t="shared" si="7"/>
+        <v>9000</v>
+      </c>
+      <c r="W48">
+        <f t="shared" si="8"/>
+        <v>9000</v>
+      </c>
+    </row>
+    <row r="49" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A49">
         <v>1047</v>
       </c>
@@ -10714,19 +11404,31 @@
         <v>ниже середины</v>
       </c>
       <c r="R49">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="S49">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>144000</v>
       </c>
       <c r="T49">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>7000</v>
       </c>
-    </row>
-    <row r="50" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U49">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V49">
+        <f t="shared" si="7"/>
+        <v>7000</v>
+      </c>
+      <c r="W49">
+        <f t="shared" si="8"/>
+        <v>7000</v>
+      </c>
+    </row>
+    <row r="50" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A50">
         <v>1048</v>
       </c>
@@ -10780,19 +11482,31 @@
         <v>выше середины</v>
       </c>
       <c r="R50">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="S50">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>169000</v>
       </c>
       <c r="T50">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="51" spans="1:20" x14ac:dyDescent="0.2">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="U50">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V50">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="W50">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A51">
         <v>1049</v>
       </c>
@@ -10846,19 +11560,31 @@
         <v>выше середины</v>
       </c>
       <c r="R51">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="S51">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>174000</v>
       </c>
       <c r="T51">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="52" spans="1:20" x14ac:dyDescent="0.2">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="U51">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V51">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="W51">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A52">
         <v>1050</v>
       </c>
@@ -10912,19 +11638,31 @@
         <v>выше середины</v>
       </c>
       <c r="R52">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="S52">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>175000</v>
       </c>
       <c r="T52">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="53" spans="1:20" x14ac:dyDescent="0.2">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="U52">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V52">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="W52">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A53">
         <v>1051</v>
       </c>
@@ -10978,19 +11716,31 @@
         <v>выше середины</v>
       </c>
       <c r="R53">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="S53">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>168000</v>
       </c>
       <c r="T53">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="54" spans="1:20" x14ac:dyDescent="0.2">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="U53">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V53">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="W53">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A54">
         <v>1052</v>
       </c>
@@ -11044,19 +11794,31 @@
         <v>ниже середины</v>
       </c>
       <c r="R54">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="S54">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>153000</v>
       </c>
       <c r="T54">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>7000</v>
       </c>
-    </row>
-    <row r="55" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U54">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V54">
+        <f t="shared" si="7"/>
+        <v>4200</v>
+      </c>
+      <c r="W54">
+        <f t="shared" si="8"/>
+        <v>4200</v>
+      </c>
+    </row>
+    <row r="55" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A55">
         <v>1053</v>
       </c>
@@ -11110,19 +11872,31 @@
         <v>выше середины</v>
       </c>
       <c r="R55">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="S55">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>191000</v>
       </c>
       <c r="T55">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="56" spans="1:20" x14ac:dyDescent="0.2">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="U55">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V55">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="W55">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A56">
         <v>1054</v>
       </c>
@@ -11176,19 +11950,31 @@
         <v>выше середины</v>
       </c>
       <c r="R56">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="S56">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>182000</v>
       </c>
       <c r="T56">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="57" spans="1:20" x14ac:dyDescent="0.2">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="U56">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V56">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="W56">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A57">
         <v>1055</v>
       </c>
@@ -11242,19 +12028,31 @@
         <v>ниже середины</v>
       </c>
       <c r="R57">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="S57">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>173000</v>
       </c>
       <c r="T57">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>3000</v>
       </c>
-    </row>
-    <row r="58" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U57">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V57">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="W57">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A58">
         <v>1056</v>
       </c>
@@ -11308,19 +12106,31 @@
         <v>выше середины</v>
       </c>
       <c r="R58">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="S58">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>182000</v>
       </c>
       <c r="T58">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="59" spans="1:20" x14ac:dyDescent="0.2">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="U58">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V58">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="W58">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A59">
         <v>1057</v>
       </c>
@@ -11374,19 +12184,31 @@
         <v>выше середины</v>
       </c>
       <c r="R59">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="S59">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>186000</v>
       </c>
       <c r="T59">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="60" spans="1:20" x14ac:dyDescent="0.2">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="U59">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V59">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="W59">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A60">
         <v>1058</v>
       </c>
@@ -11440,19 +12262,31 @@
         <v>ниже середины</v>
       </c>
       <c r="R60">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="S60">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>174000</v>
       </c>
       <c r="T60">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>11000</v>
       </c>
-    </row>
-    <row r="61" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U60">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V60">
+        <f t="shared" si="7"/>
+        <v>11000</v>
+      </c>
+      <c r="W60">
+        <f t="shared" si="8"/>
+        <v>11000</v>
+      </c>
+    </row>
+    <row r="61" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A61">
         <v>1059</v>
       </c>
@@ -11506,19 +12340,31 @@
         <v>выше середины</v>
       </c>
       <c r="R61">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="S61">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>189000</v>
       </c>
       <c r="T61">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="62" spans="1:20" x14ac:dyDescent="0.2">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="U61">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V61">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="W61">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A62">
         <v>1060</v>
       </c>
@@ -11572,19 +12418,31 @@
         <v>выше середины</v>
       </c>
       <c r="R62">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="S62">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>186000</v>
       </c>
       <c r="T62">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="63" spans="1:20" x14ac:dyDescent="0.2">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="U62">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V62">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="W62">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A63">
         <v>1061</v>
       </c>
@@ -11638,19 +12496,31 @@
         <v>выше середины</v>
       </c>
       <c r="R63">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="S63">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>210000</v>
       </c>
       <c r="T63">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="64" spans="1:20" x14ac:dyDescent="0.2">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="U63">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V63">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="W63">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A64">
         <v>1062</v>
       </c>
@@ -11704,19 +12574,31 @@
         <v>ниже середины</v>
       </c>
       <c r="R64">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="S64">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>140000</v>
       </c>
       <c r="T64">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>12000</v>
       </c>
-    </row>
-    <row r="65" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U64">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V64">
+        <f t="shared" si="7"/>
+        <v>12000</v>
+      </c>
+      <c r="W64">
+        <f t="shared" si="8"/>
+        <v>12000</v>
+      </c>
+    </row>
+    <row r="65" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A65">
         <v>1063</v>
       </c>
@@ -11770,19 +12652,31 @@
         <v>ниже середины</v>
       </c>
       <c r="R65">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="S65">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>138000</v>
       </c>
       <c r="T65">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>14000</v>
       </c>
-    </row>
-    <row r="66" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U65">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V65">
+        <f t="shared" si="7"/>
+        <v>11200</v>
+      </c>
+      <c r="W65">
+        <f t="shared" si="8"/>
+        <v>11200</v>
+      </c>
+    </row>
+    <row r="66" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A66">
         <v>1064</v>
       </c>
@@ -11836,19 +12730,31 @@
         <v>выше середины</v>
       </c>
       <c r="R66">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="S66">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>161000</v>
       </c>
       <c r="T66">
-        <f t="shared" ref="T66:T97" si="4">IF(S66&lt;O66,O66-S66,0)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="67" spans="1:20" x14ac:dyDescent="0.2">
+        <f t="shared" ref="T66:T97" si="9">IF(S66&lt;O66,O66-S66,0)</f>
+        <v>0</v>
+      </c>
+      <c r="U66">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V66">
+        <f t="shared" ref="V66:V97" si="10">IF(AND(R66=0, T66&gt;3000), T66*J66, 0)</f>
+        <v>0</v>
+      </c>
+      <c r="W66">
+        <f t="shared" ref="W66:W97" si="11">U66+V66</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A67">
         <v>1065</v>
       </c>
@@ -11902,19 +12808,31 @@
         <v>ниже середины</v>
       </c>
       <c r="R67">
-        <f t="shared" ref="R67:R123" si="5">IF(S67&lt;N67,N67-S67,0)</f>
+        <f t="shared" ref="R67:R123" si="12">IF(S67&lt;N67,N67-S67,0)</f>
         <v>0</v>
       </c>
       <c r="S67">
-        <f t="shared" ref="S67:S123" si="6">K67/J67</f>
+        <f t="shared" ref="S67:S123" si="13">K67/J67</f>
         <v>148000</v>
       </c>
       <c r="T67">
-        <f t="shared" si="4"/>
+        <f t="shared" si="9"/>
         <v>12000</v>
       </c>
-    </row>
-    <row r="68" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U67">
+        <f t="shared" ref="U67:U123" si="14">IF(R67&gt;0, R67*J67, 0)</f>
+        <v>0</v>
+      </c>
+      <c r="V67">
+        <f t="shared" si="10"/>
+        <v>12000</v>
+      </c>
+      <c r="W67">
+        <f t="shared" si="11"/>
+        <v>12000</v>
+      </c>
+    </row>
+    <row r="68" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A68">
         <v>1066</v>
       </c>
@@ -11968,19 +12886,31 @@
         <v>выше середины</v>
       </c>
       <c r="R68">
-        <f t="shared" si="5"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="S68">
-        <f t="shared" si="6"/>
+        <f t="shared" si="13"/>
         <v>183000</v>
       </c>
       <c r="T68">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="69" spans="1:20" x14ac:dyDescent="0.2">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="U68">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="V68">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="W68">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A69">
         <v>1067</v>
       </c>
@@ -12034,19 +12964,31 @@
         <v>ниже середины</v>
       </c>
       <c r="R69">
-        <f t="shared" si="5"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="S69">
-        <f t="shared" si="6"/>
+        <f t="shared" si="13"/>
         <v>158000</v>
       </c>
       <c r="T69">
-        <f t="shared" si="4"/>
+        <f t="shared" si="9"/>
         <v>2000</v>
       </c>
-    </row>
-    <row r="70" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U69">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="V69">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="W69">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A70">
         <v>1068</v>
       </c>
@@ -12100,19 +13042,31 @@
         <v>выше середины</v>
       </c>
       <c r="R70">
-        <f t="shared" si="5"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="S70">
-        <f t="shared" si="6"/>
+        <f t="shared" si="13"/>
         <v>179000</v>
       </c>
       <c r="T70">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="71" spans="1:20" x14ac:dyDescent="0.2">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="U70">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="V70">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="W70">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A71">
         <v>1069</v>
       </c>
@@ -12166,19 +13120,31 @@
         <v>ниже середины</v>
       </c>
       <c r="R71">
-        <f t="shared" si="5"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="S71">
-        <f t="shared" si="6"/>
+        <f t="shared" si="13"/>
         <v>150000</v>
       </c>
       <c r="T71">
-        <f t="shared" si="4"/>
+        <f t="shared" si="9"/>
         <v>18000</v>
       </c>
-    </row>
-    <row r="72" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U71">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="V71">
+        <f t="shared" si="10"/>
+        <v>5400</v>
+      </c>
+      <c r="W71">
+        <f t="shared" si="11"/>
+        <v>5400</v>
+      </c>
+    </row>
+    <row r="72" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A72">
         <v>1070</v>
       </c>
@@ -12232,19 +13198,31 @@
         <v>ниже середины</v>
       </c>
       <c r="R72">
-        <f t="shared" si="5"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="S72">
-        <f t="shared" si="6"/>
+        <f t="shared" si="13"/>
         <v>163000</v>
       </c>
       <c r="T72">
-        <f t="shared" si="4"/>
+        <f t="shared" si="9"/>
         <v>5000</v>
       </c>
-    </row>
-    <row r="73" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U72">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="V72">
+        <f t="shared" si="10"/>
+        <v>5000</v>
+      </c>
+      <c r="W72">
+        <f t="shared" si="11"/>
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="73" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A73">
         <v>1071</v>
       </c>
@@ -12298,19 +13276,31 @@
         <v>выше середины</v>
       </c>
       <c r="R73">
-        <f t="shared" si="5"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="S73">
-        <f t="shared" si="6"/>
+        <f t="shared" si="13"/>
         <v>190000</v>
       </c>
       <c r="T73">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="74" spans="1:20" x14ac:dyDescent="0.2">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="U73">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="V73">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="W73">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A74">
         <v>1072</v>
       </c>
@@ -12364,19 +13354,31 @@
         <v>выше середины</v>
       </c>
       <c r="R74">
-        <f t="shared" si="5"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="S74">
-        <f t="shared" si="6"/>
+        <f t="shared" si="13"/>
         <v>189000</v>
       </c>
       <c r="T74">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="75" spans="1:20" x14ac:dyDescent="0.2">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="U74">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="V74">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="W74">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A75">
         <v>1073</v>
       </c>
@@ -12430,19 +13432,31 @@
         <v>ниже середины</v>
       </c>
       <c r="R75">
-        <f t="shared" si="5"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="S75">
-        <f t="shared" si="6"/>
+        <f t="shared" si="13"/>
         <v>175000</v>
       </c>
       <c r="T75">
-        <f t="shared" si="4"/>
+        <f t="shared" si="9"/>
         <v>1000</v>
       </c>
-    </row>
-    <row r="76" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U75">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="V75">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="W75">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A76">
         <v>1074</v>
       </c>
@@ -12496,19 +13510,31 @@
         <v>выше середины</v>
       </c>
       <c r="R76">
-        <f t="shared" si="5"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="S76">
-        <f t="shared" si="6"/>
+        <f t="shared" si="13"/>
         <v>123000</v>
       </c>
       <c r="T76">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="77" spans="1:20" x14ac:dyDescent="0.2">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="U76">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="V76">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="W76">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A77">
         <v>1075</v>
       </c>
@@ -12562,19 +13588,31 @@
         <v>ниже середины</v>
       </c>
       <c r="R77">
-        <f t="shared" si="5"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="S77">
-        <f t="shared" si="6"/>
+        <f t="shared" si="13"/>
         <v>121000</v>
       </c>
       <c r="T77">
-        <f t="shared" si="4"/>
+        <f t="shared" si="9"/>
         <v>1000</v>
       </c>
-    </row>
-    <row r="78" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U77">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="V77">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="W77">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A78">
         <v>1076</v>
       </c>
@@ -12628,19 +13666,31 @@
         <v>ниже середины</v>
       </c>
       <c r="R78">
-        <f t="shared" si="5"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="S78">
-        <f t="shared" si="6"/>
+        <f t="shared" si="13"/>
         <v>116000</v>
       </c>
       <c r="T78">
-        <f t="shared" si="4"/>
+        <f t="shared" si="9"/>
         <v>6000</v>
       </c>
-    </row>
-    <row r="79" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U78">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="V78">
+        <f t="shared" si="10"/>
+        <v>6000</v>
+      </c>
+      <c r="W78">
+        <f t="shared" si="11"/>
+        <v>6000</v>
+      </c>
+    </row>
+    <row r="79" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A79">
         <v>1077</v>
       </c>
@@ -12694,19 +13744,31 @@
         <v>выше середины</v>
       </c>
       <c r="R79">
-        <f t="shared" si="5"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="S79">
-        <f t="shared" si="6"/>
+        <f t="shared" si="13"/>
         <v>140000</v>
       </c>
       <c r="T79">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="80" spans="1:20" x14ac:dyDescent="0.2">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="U79">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="V79">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="W79">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A80">
         <v>1078</v>
       </c>
@@ -12760,19 +13822,31 @@
         <v>выше середины</v>
       </c>
       <c r="R80">
-        <f t="shared" si="5"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="S80">
-        <f t="shared" si="6"/>
+        <f t="shared" si="13"/>
         <v>140000</v>
       </c>
       <c r="T80">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="81" spans="1:20" x14ac:dyDescent="0.2">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="U80">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="V80">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="W80">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A81">
         <v>1079</v>
       </c>
@@ -12826,19 +13900,31 @@
         <v>ниже середины</v>
       </c>
       <c r="R81">
-        <f t="shared" si="5"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="S81">
-        <f t="shared" si="6"/>
+        <f t="shared" si="13"/>
         <v>129000</v>
       </c>
       <c r="T81">
-        <f t="shared" si="4"/>
+        <f t="shared" si="9"/>
         <v>1000</v>
       </c>
-    </row>
-    <row r="82" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U81">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="V81">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="W81">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A82">
         <v>1080</v>
       </c>
@@ -12892,19 +13978,31 @@
         <v>выше середины</v>
       </c>
       <c r="R82">
-        <f t="shared" si="5"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="S82">
-        <f t="shared" si="6"/>
+        <f t="shared" si="13"/>
         <v>142000</v>
       </c>
       <c r="T82">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="83" spans="1:20" x14ac:dyDescent="0.2">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="U82">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="V82">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="W82">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A83">
         <v>1081</v>
       </c>
@@ -12958,19 +14056,31 @@
         <v>выше середины</v>
       </c>
       <c r="R83">
-        <f t="shared" si="5"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="S83">
-        <f t="shared" si="6"/>
+        <f t="shared" si="13"/>
         <v>155000</v>
       </c>
       <c r="T83">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="84" spans="1:20" x14ac:dyDescent="0.2">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="U83">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="V83">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="W83">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A84">
         <v>1082</v>
       </c>
@@ -13024,19 +14134,31 @@
         <v>выше середины</v>
       </c>
       <c r="R84">
-        <f t="shared" si="5"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="S84">
-        <f t="shared" si="6"/>
+        <f t="shared" si="13"/>
         <v>151000</v>
       </c>
       <c r="T84">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="85" spans="1:20" x14ac:dyDescent="0.2">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="U84">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="V84">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="W84">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A85">
         <v>1083</v>
       </c>
@@ -13090,19 +14212,31 @@
         <v>ниже середины</v>
       </c>
       <c r="R85">
-        <f t="shared" si="5"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="S85">
-        <f t="shared" si="6"/>
+        <f t="shared" si="13"/>
         <v>141000</v>
       </c>
       <c r="T85">
-        <f t="shared" si="4"/>
+        <f t="shared" si="9"/>
         <v>3000</v>
       </c>
-    </row>
-    <row r="86" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U85">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="V85">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="W85">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A86">
         <v>1084</v>
       </c>
@@ -13156,19 +14290,31 @@
         <v>ниже середины</v>
       </c>
       <c r="R86">
-        <f t="shared" si="5"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="S86">
-        <f t="shared" si="6"/>
+        <f t="shared" si="13"/>
         <v>127000</v>
       </c>
       <c r="T86">
-        <f t="shared" si="4"/>
+        <f t="shared" si="9"/>
         <v>17000</v>
       </c>
-    </row>
-    <row r="87" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U86">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="V86">
+        <f t="shared" si="10"/>
+        <v>12750</v>
+      </c>
+      <c r="W86">
+        <f t="shared" si="11"/>
+        <v>12750</v>
+      </c>
+    </row>
+    <row r="87" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A87">
         <v>1085</v>
       </c>
@@ -13222,19 +14368,31 @@
         <v>выше середины</v>
       </c>
       <c r="R87">
-        <f t="shared" si="5"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="S87">
-        <f t="shared" si="6"/>
+        <f t="shared" si="13"/>
         <v>156000</v>
       </c>
       <c r="T87">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="88" spans="1:20" x14ac:dyDescent="0.2">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="U87">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="V87">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="W87">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A88">
         <v>1086</v>
       </c>
@@ -13288,19 +14446,31 @@
         <v>ниже середины</v>
       </c>
       <c r="R88">
-        <f t="shared" si="5"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="S88">
-        <f t="shared" si="6"/>
+        <f t="shared" si="13"/>
         <v>139000</v>
       </c>
       <c r="T88">
-        <f t="shared" si="4"/>
+        <f t="shared" si="9"/>
         <v>12000</v>
       </c>
-    </row>
-    <row r="89" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U88">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="V88">
+        <f t="shared" si="10"/>
+        <v>12000</v>
+      </c>
+      <c r="W88">
+        <f t="shared" si="11"/>
+        <v>12000</v>
+      </c>
+    </row>
+    <row r="89" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A89">
         <v>1087</v>
       </c>
@@ -13354,19 +14524,31 @@
         <v>выше середины</v>
       </c>
       <c r="R89">
-        <f t="shared" si="5"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="S89">
-        <f t="shared" si="6"/>
+        <f t="shared" si="13"/>
         <v>156000</v>
       </c>
       <c r="T89">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="90" spans="1:20" x14ac:dyDescent="0.2">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="U89">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="V89">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="W89">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A90">
         <v>1088</v>
       </c>
@@ -13420,19 +14602,31 @@
         <v>ниже середины</v>
       </c>
       <c r="R90">
-        <f t="shared" si="5"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="S90">
-        <f t="shared" si="6"/>
+        <f t="shared" si="13"/>
         <v>150000</v>
       </c>
       <c r="T90">
-        <f t="shared" si="4"/>
+        <f t="shared" si="9"/>
         <v>1000</v>
       </c>
-    </row>
-    <row r="91" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U90">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="V90">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="W90">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A91">
         <v>1089</v>
       </c>
@@ -13481,24 +14675,35 @@
         <f>SUMIFS(salary_bands[salary_max],salary_bands[prof_group],G91,salary_bands[grade],I91)</f>
         <v>0</v>
       </c>
-      <c r="Q91" t="str" cm="1">
-        <f t="array" ref="Q91">_xlfn.IFS(S91&lt;N91,"ниже минимума",S91&lt;=O91,"ниже середины",S91&lt;=P91,"выше середины",S91&gt;P91,"выше максимума")</f>
-        <v>выше максимума</v>
+      <c r="Q91" t="s">
+        <v>179</v>
       </c>
       <c r="R91">
-        <f t="shared" si="5"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="S91">
-        <f t="shared" si="6"/>
+        <f t="shared" si="13"/>
         <v>110000</v>
       </c>
       <c r="T91">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="92" spans="1:20" x14ac:dyDescent="0.2">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="U91">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="V91">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="W91">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A92">
         <v>1090</v>
       </c>
@@ -13547,24 +14752,35 @@
         <f>SUMIFS(salary_bands[salary_max],salary_bands[prof_group],G92,salary_bands[grade],I92)</f>
         <v>0</v>
       </c>
-      <c r="Q92" t="str" cm="1">
-        <f t="array" ref="Q92">_xlfn.IFS(S92&lt;N92,"ниже минимума",S92&lt;=O92,"ниже середины",S92&lt;=P92,"выше середины",S92&gt;P92,"выше максимума")</f>
-        <v>выше максимума</v>
+      <c r="Q92" t="s">
+        <v>179</v>
       </c>
       <c r="R92">
-        <f t="shared" si="5"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="S92">
-        <f t="shared" si="6"/>
+        <f t="shared" si="13"/>
         <v>117000</v>
       </c>
       <c r="T92">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="93" spans="1:20" x14ac:dyDescent="0.2">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="U92">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="V92">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="W92">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A93">
         <v>1091</v>
       </c>
@@ -13613,24 +14829,35 @@
         <f>SUMIFS(salary_bands[salary_max],salary_bands[prof_group],G93,salary_bands[grade],I93)</f>
         <v>0</v>
       </c>
-      <c r="Q93" t="str" cm="1">
-        <f t="array" ref="Q93">_xlfn.IFS(S93&lt;N93,"ниже минимума",S93&lt;=O93,"ниже середины",S93&lt;=P93,"выше середины",S93&gt;P93,"выше максимума")</f>
-        <v>выше максимума</v>
+      <c r="Q93" t="s">
+        <v>179</v>
       </c>
       <c r="R93">
-        <f t="shared" si="5"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="S93">
-        <f t="shared" si="6"/>
+        <f t="shared" si="13"/>
         <v>100000</v>
       </c>
       <c r="T93">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="94" spans="1:20" x14ac:dyDescent="0.2">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="U93">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="V93">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="W93">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A94">
         <v>1092</v>
       </c>
@@ -13684,19 +14911,31 @@
         <v>выше середины</v>
       </c>
       <c r="R94">
-        <f t="shared" si="5"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="S94">
-        <f t="shared" si="6"/>
+        <f t="shared" si="13"/>
         <v>123000</v>
       </c>
       <c r="T94">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="95" spans="1:20" x14ac:dyDescent="0.2">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="U94">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="V94">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="W94">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A95">
         <v>1093</v>
       </c>
@@ -13750,19 +14989,31 @@
         <v>ниже середины</v>
       </c>
       <c r="R95">
-        <f t="shared" si="5"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="S95">
-        <f t="shared" si="6"/>
+        <f t="shared" si="13"/>
         <v>106000</v>
       </c>
       <c r="T95">
-        <f t="shared" si="4"/>
+        <f t="shared" si="9"/>
         <v>9000</v>
       </c>
-    </row>
-    <row r="96" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U95">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="V95">
+        <f t="shared" si="10"/>
+        <v>9000</v>
+      </c>
+      <c r="W95">
+        <f t="shared" si="11"/>
+        <v>9000</v>
+      </c>
+    </row>
+    <row r="96" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A96">
         <v>1094</v>
       </c>
@@ -13816,19 +15067,31 @@
         <v>выше середины</v>
       </c>
       <c r="R96">
-        <f t="shared" si="5"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="S96">
-        <f t="shared" si="6"/>
+        <f t="shared" si="13"/>
         <v>123000</v>
       </c>
       <c r="T96">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="97" spans="1:20" x14ac:dyDescent="0.2">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="U96">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="V96">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="W96">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A97">
         <v>1095</v>
       </c>
@@ -13882,19 +15145,31 @@
         <v>ниже середины</v>
       </c>
       <c r="R97">
-        <f t="shared" si="5"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="S97">
-        <f t="shared" si="6"/>
+        <f t="shared" si="13"/>
         <v>110000</v>
       </c>
       <c r="T97">
-        <f t="shared" si="4"/>
+        <f t="shared" si="9"/>
         <v>5000</v>
       </c>
-    </row>
-    <row r="98" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U97">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="V97">
+        <f t="shared" si="10"/>
+        <v>5000</v>
+      </c>
+      <c r="W97">
+        <f t="shared" si="11"/>
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="98" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A98">
         <v>1096</v>
       </c>
@@ -13948,19 +15223,31 @@
         <v>ниже середины</v>
       </c>
       <c r="R98">
-        <f t="shared" si="5"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="S98">
-        <f t="shared" si="6"/>
+        <f t="shared" si="13"/>
         <v>115000</v>
       </c>
       <c r="T98">
-        <f t="shared" ref="T98:T123" si="7">IF(S98&lt;O98,O98-S98,0)</f>
+        <f t="shared" ref="T98:T123" si="15">IF(S98&lt;O98,O98-S98,0)</f>
         <v>7000</v>
       </c>
-    </row>
-    <row r="99" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U98">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="V98">
+        <f t="shared" ref="V98:V123" si="16">IF(AND(R98=0, T98&gt;3000), T98*J98, 0)</f>
+        <v>5600</v>
+      </c>
+      <c r="W98">
+        <f t="shared" ref="W98:W123" si="17">U98+V98</f>
+        <v>5600</v>
+      </c>
+    </row>
+    <row r="99" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A99">
         <v>1097</v>
       </c>
@@ -14014,19 +15301,31 @@
         <v>ниже середины</v>
       </c>
       <c r="R99">
-        <f t="shared" si="5"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="S99">
-        <f t="shared" si="6"/>
+        <f t="shared" si="13"/>
         <v>121000</v>
       </c>
       <c r="T99">
-        <f t="shared" si="7"/>
+        <f t="shared" si="15"/>
         <v>1000</v>
       </c>
-    </row>
-    <row r="100" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U99">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="V99">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="W99">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A100">
         <v>1098</v>
       </c>
@@ -14080,19 +15379,31 @@
         <v>выше середины</v>
       </c>
       <c r="R100">
-        <f t="shared" si="5"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="S100">
-        <f t="shared" si="6"/>
+        <f t="shared" si="13"/>
         <v>135000</v>
       </c>
       <c r="T100">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101" spans="1:20" x14ac:dyDescent="0.2">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+      <c r="U100">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="V100">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="W100">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A101">
         <v>1099</v>
       </c>
@@ -14146,19 +15457,31 @@
         <v>выше середины</v>
       </c>
       <c r="R101">
-        <f t="shared" si="5"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="S101">
-        <f t="shared" si="6"/>
+        <f t="shared" si="13"/>
         <v>135000</v>
       </c>
       <c r="T101">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="102" spans="1:20" x14ac:dyDescent="0.2">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+      <c r="U101">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="V101">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="W101">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A102">
         <v>1100</v>
       </c>
@@ -14212,19 +15535,31 @@
         <v>выше середины</v>
       </c>
       <c r="R102">
-        <f t="shared" si="5"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="S102">
-        <f t="shared" si="6"/>
+        <f t="shared" si="13"/>
         <v>130000</v>
       </c>
       <c r="T102">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="103" spans="1:20" x14ac:dyDescent="0.2">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+      <c r="U102">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="V102">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="W102">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="103" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A103">
         <v>1101</v>
       </c>
@@ -14278,19 +15613,31 @@
         <v>выше середины</v>
       </c>
       <c r="R103">
-        <f t="shared" si="5"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="S103">
-        <f t="shared" si="6"/>
+        <f t="shared" si="13"/>
         <v>142000</v>
       </c>
       <c r="T103">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="104" spans="1:20" x14ac:dyDescent="0.2">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+      <c r="U103">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="V103">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="W103">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="104" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A104">
         <v>1102</v>
       </c>
@@ -14344,19 +15691,31 @@
         <v>выше середины</v>
       </c>
       <c r="R104">
-        <f t="shared" si="5"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="S104">
-        <f t="shared" si="6"/>
+        <f t="shared" si="13"/>
         <v>133000</v>
       </c>
       <c r="T104">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="105" spans="1:20" x14ac:dyDescent="0.2">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+      <c r="U104">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="V104">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="W104">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="105" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A105">
         <v>1103</v>
       </c>
@@ -14410,19 +15769,31 @@
         <v>ниже минимума</v>
       </c>
       <c r="R105">
-        <f t="shared" si="5"/>
+        <f t="shared" si="12"/>
         <v>38000</v>
       </c>
       <c r="S105">
-        <f t="shared" si="6"/>
+        <f t="shared" si="13"/>
         <v>132000</v>
       </c>
       <c r="T105">
-        <f t="shared" si="7"/>
+        <f t="shared" si="15"/>
         <v>68000</v>
       </c>
-    </row>
-    <row r="106" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U105">
+        <f t="shared" si="14"/>
+        <v>38000</v>
+      </c>
+      <c r="V105">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="W105">
+        <f t="shared" si="17"/>
+        <v>38000</v>
+      </c>
+    </row>
+    <row r="106" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A106">
         <v>1104</v>
       </c>
@@ -14476,19 +15847,31 @@
         <v>ниже минимума</v>
       </c>
       <c r="R106">
-        <f t="shared" si="5"/>
+        <f t="shared" si="12"/>
         <v>35000</v>
       </c>
       <c r="S106">
-        <f t="shared" si="6"/>
+        <f t="shared" si="13"/>
         <v>121000</v>
       </c>
       <c r="T106">
-        <f t="shared" si="7"/>
+        <f t="shared" si="15"/>
         <v>63000</v>
       </c>
-    </row>
-    <row r="107" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U106">
+        <f t="shared" si="14"/>
+        <v>35000</v>
+      </c>
+      <c r="V106">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="W106">
+        <f t="shared" si="17"/>
+        <v>35000</v>
+      </c>
+    </row>
+    <row r="107" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A107">
         <v>1105</v>
       </c>
@@ -14542,19 +15925,31 @@
         <v>ниже минимума</v>
       </c>
       <c r="R107">
-        <f t="shared" si="5"/>
+        <f t="shared" si="12"/>
         <v>27000</v>
       </c>
       <c r="S107">
-        <f t="shared" si="6"/>
+        <f t="shared" si="13"/>
         <v>123000</v>
       </c>
       <c r="T107">
-        <f t="shared" si="7"/>
+        <f t="shared" si="15"/>
         <v>53000</v>
       </c>
-    </row>
-    <row r="108" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U107">
+        <f t="shared" si="14"/>
+        <v>27000</v>
+      </c>
+      <c r="V107">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="W107">
+        <f t="shared" si="17"/>
+        <v>27000</v>
+      </c>
+    </row>
+    <row r="108" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A108">
         <v>1106</v>
       </c>
@@ -14608,19 +16003,31 @@
         <v>ниже минимума</v>
       </c>
       <c r="R108">
-        <f t="shared" si="5"/>
+        <f t="shared" si="12"/>
         <v>30000</v>
       </c>
       <c r="S108">
-        <f t="shared" si="6"/>
+        <f t="shared" si="13"/>
         <v>113000</v>
       </c>
       <c r="T108">
-        <f t="shared" si="7"/>
+        <f t="shared" si="15"/>
         <v>55000</v>
       </c>
-    </row>
-    <row r="109" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U108">
+        <f t="shared" si="14"/>
+        <v>30000</v>
+      </c>
+      <c r="V108">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="W108">
+        <f t="shared" si="17"/>
+        <v>30000</v>
+      </c>
+    </row>
+    <row r="109" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A109">
         <v>1107</v>
       </c>
@@ -14674,19 +16081,31 @@
         <v>ниже минимума</v>
       </c>
       <c r="R109">
-        <f t="shared" si="5"/>
+        <f t="shared" si="12"/>
         <v>28000</v>
       </c>
       <c r="S109">
-        <f t="shared" si="6"/>
+        <f t="shared" si="13"/>
         <v>108000</v>
       </c>
       <c r="T109">
-        <f t="shared" si="7"/>
+        <f t="shared" si="15"/>
         <v>52000</v>
       </c>
-    </row>
-    <row r="110" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U109">
+        <f t="shared" si="14"/>
+        <v>28000</v>
+      </c>
+      <c r="V109">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="W109">
+        <f t="shared" si="17"/>
+        <v>28000</v>
+      </c>
+    </row>
+    <row r="110" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A110">
         <v>1108</v>
       </c>
@@ -14740,19 +16159,31 @@
         <v>ниже минимума</v>
       </c>
       <c r="R110">
-        <f t="shared" si="5"/>
+        <f t="shared" si="12"/>
         <v>17000</v>
       </c>
       <c r="S110">
-        <f t="shared" si="6"/>
+        <f t="shared" si="13"/>
         <v>99000</v>
       </c>
       <c r="T110">
-        <f t="shared" si="7"/>
+        <f t="shared" si="15"/>
         <v>38000</v>
       </c>
-    </row>
-    <row r="111" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U110">
+        <f t="shared" si="14"/>
+        <v>17000</v>
+      </c>
+      <c r="V110">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="W110">
+        <f t="shared" si="17"/>
+        <v>17000</v>
+      </c>
+    </row>
+    <row r="111" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A111">
         <v>1109</v>
       </c>
@@ -14806,19 +16237,31 @@
         <v>ниже минимума</v>
       </c>
       <c r="R111">
-        <f t="shared" si="5"/>
+        <f t="shared" si="12"/>
         <v>23000</v>
       </c>
       <c r="S111">
-        <f t="shared" si="6"/>
+        <f t="shared" si="13"/>
         <v>75000</v>
       </c>
       <c r="T111">
-        <f t="shared" si="7"/>
+        <f t="shared" si="15"/>
         <v>40000</v>
       </c>
-    </row>
-    <row r="112" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U111">
+        <f t="shared" si="14"/>
+        <v>23000</v>
+      </c>
+      <c r="V111">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="W111">
+        <f t="shared" si="17"/>
+        <v>23000</v>
+      </c>
+    </row>
+    <row r="112" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A112">
         <v>1110</v>
       </c>
@@ -14872,19 +16315,31 @@
         <v>ниже минимума</v>
       </c>
       <c r="R112">
-        <f t="shared" si="5"/>
+        <f t="shared" si="12"/>
         <v>28000</v>
       </c>
       <c r="S112">
-        <f t="shared" si="6"/>
+        <f t="shared" si="13"/>
         <v>128000</v>
       </c>
       <c r="T112">
-        <f t="shared" si="7"/>
+        <f t="shared" si="15"/>
         <v>56000</v>
       </c>
-    </row>
-    <row r="113" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U112">
+        <f t="shared" si="14"/>
+        <v>14000</v>
+      </c>
+      <c r="V112">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="W112">
+        <f t="shared" si="17"/>
+        <v>14000</v>
+      </c>
+    </row>
+    <row r="113" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A113">
         <v>1111</v>
       </c>
@@ -14938,19 +16393,31 @@
         <v>выше середины</v>
       </c>
       <c r="R113">
-        <f t="shared" si="5"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="S113">
-        <f t="shared" si="6"/>
+        <f t="shared" si="13"/>
         <v>230000</v>
       </c>
       <c r="T113">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="114" spans="1:20" x14ac:dyDescent="0.2">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+      <c r="U113">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="V113">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="W113">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="114" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A114">
         <v>1112</v>
       </c>
@@ -15004,19 +16471,31 @@
         <v>ниже середины</v>
       </c>
       <c r="R114">
-        <f t="shared" si="5"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="S114">
-        <f t="shared" si="6"/>
+        <f t="shared" si="13"/>
         <v>210000</v>
       </c>
       <c r="T114">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="115" spans="1:20" x14ac:dyDescent="0.2">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+      <c r="U114">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="V114">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="W114">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="115" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A115">
         <v>1113</v>
       </c>
@@ -15070,19 +16549,31 @@
         <v>ниже середины</v>
       </c>
       <c r="R115">
-        <f t="shared" si="5"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="S115">
-        <f t="shared" si="6"/>
+        <f t="shared" si="13"/>
         <v>194000</v>
       </c>
       <c r="T115">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="116" spans="1:20" x14ac:dyDescent="0.2">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+      <c r="U115">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="V115">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="W115">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="116" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A116">
         <v>1114</v>
       </c>
@@ -15139,19 +16630,31 @@
         <v>ниже середины</v>
       </c>
       <c r="R116">
-        <f t="shared" si="5"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="S116">
-        <f t="shared" si="6"/>
+        <f t="shared" si="13"/>
         <v>202000</v>
       </c>
       <c r="T116">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="117" spans="1:20" x14ac:dyDescent="0.2">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+      <c r="U116">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="V116">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="W116">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="117" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A117">
         <v>1115</v>
       </c>
@@ -15205,19 +16708,31 @@
         <v>ниже минимума</v>
       </c>
       <c r="R117">
-        <f t="shared" si="5"/>
+        <f t="shared" si="12"/>
         <v>44000</v>
       </c>
       <c r="S117">
-        <f t="shared" si="6"/>
+        <f t="shared" si="13"/>
         <v>92000</v>
       </c>
       <c r="T117">
-        <f t="shared" si="7"/>
+        <f t="shared" si="15"/>
         <v>68000</v>
       </c>
-    </row>
-    <row r="118" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U117">
+        <f t="shared" si="14"/>
+        <v>44000</v>
+      </c>
+      <c r="V117">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="W117">
+        <f t="shared" si="17"/>
+        <v>44000</v>
+      </c>
+    </row>
+    <row r="118" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A118">
         <v>1116</v>
       </c>
@@ -15271,19 +16786,31 @@
         <v>выше максимума</v>
       </c>
       <c r="R118">
-        <f t="shared" si="5"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="S118">
-        <f t="shared" si="6"/>
+        <f t="shared" si="13"/>
         <v>210000</v>
       </c>
       <c r="T118">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="119" spans="1:20" x14ac:dyDescent="0.2">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+      <c r="U118">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="V118">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="W118">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="119" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A119">
         <v>1117</v>
       </c>
@@ -15337,19 +16864,31 @@
         <v>ниже середины</v>
       </c>
       <c r="R119">
-        <f t="shared" si="5"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="S119">
-        <f t="shared" si="6"/>
+        <f t="shared" si="13"/>
         <v>160000</v>
       </c>
       <c r="T119">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="120" spans="1:20" x14ac:dyDescent="0.2">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+      <c r="U119">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="V119">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="W119">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="120" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A120">
         <v>1118</v>
       </c>
@@ -15403,19 +16942,31 @@
         <v>ниже середины</v>
       </c>
       <c r="R120">
-        <f t="shared" si="5"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="S120">
-        <f t="shared" si="6"/>
+        <f t="shared" si="13"/>
         <v>122000</v>
       </c>
       <c r="T120">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="121" spans="1:20" x14ac:dyDescent="0.2">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+      <c r="U120">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="V120">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="W120">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="121" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A121">
         <v>1119</v>
       </c>
@@ -15469,19 +17020,31 @@
         <v>выше середины</v>
       </c>
       <c r="R121">
-        <f t="shared" si="5"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="S121">
-        <f t="shared" si="6"/>
+        <f t="shared" si="13"/>
         <v>127000</v>
       </c>
       <c r="T121">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="122" spans="1:20" x14ac:dyDescent="0.2">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+      <c r="U121">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="V121">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="W121">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="122" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A122">
         <v>1120</v>
       </c>
@@ -15535,19 +17098,31 @@
         <v>ниже середины</v>
       </c>
       <c r="R122">
-        <f t="shared" si="5"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="S122">
-        <f t="shared" si="6"/>
+        <f t="shared" si="13"/>
         <v>184000</v>
       </c>
       <c r="T122">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="123" spans="1:20" x14ac:dyDescent="0.2">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+      <c r="U122">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="V122">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="W122">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="123" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A123">
         <v>1121</v>
       </c>
@@ -15601,21 +17176,33 @@
         <v>ниже середины</v>
       </c>
       <c r="R123">
-        <f t="shared" si="5"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="S123">
-        <f t="shared" si="6"/>
+        <f t="shared" si="13"/>
         <v>137000</v>
       </c>
       <c r="T123">
-        <f t="shared" si="7"/>
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+      <c r="U123">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="V123">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="W123">
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
     </row>
   </sheetData>
   <conditionalFormatting sqref="Q1:Q1048576">
-    <cfRule type="containsText" dxfId="0" priority="1" operator="containsText" text="ниже минимума">
+    <cfRule type="containsText" dxfId="8" priority="1" operator="containsText" text="ниже минимума">
       <formula>NOT(ISERROR(SEARCH("ниже минимума",Q1)))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -15628,1868 +17215,1051 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{94908A09-FE70-304B-AB6A-C01ECBFE1244}">
-  <dimension ref="A1:I65"/>
+  <dimension ref="A1:P65"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="33.6640625" customWidth="1"/>
+    <col min="1" max="1" width="46" customWidth="1"/>
     <col min="2" max="2" width="20.1640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.1640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13" customWidth="1"/>
+    <col min="4" max="4" width="15.1640625" customWidth="1"/>
     <col min="6" max="6" width="19.83203125" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="20.1640625" bestFit="1" customWidth="1"/>
     <col min="8" max="9" width="12.1640625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="20.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A1" s="4" t="s">
-        <v>158</v>
-      </c>
-      <c r="B1" s="4" t="s">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A1" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="E1" s="2" t="s">
         <v>159</v>
       </c>
-      <c r="C1" s="4" t="s">
-        <v>160</v>
-      </c>
-      <c r="D1" s="4" t="s">
-        <v>157</v>
-      </c>
-      <c r="E1" s="4" t="s">
-        <v>152</v>
-      </c>
-      <c r="F1" s="4" t="s">
-        <v>156</v>
-      </c>
-      <c r="G1" s="4" t="s">
-        <v>161</v>
-      </c>
-      <c r="H1" s="4" t="s">
-        <v>162</v>
-      </c>
-      <c r="I1" s="4" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A2" s="5" t="s">
-        <v>132</v>
-      </c>
-      <c r="B2" s="5" t="s">
+      <c r="F1" s="5"/>
+      <c r="G1" s="11"/>
+      <c r="H1" s="11"/>
+      <c r="I1" s="11"/>
+      <c r="J1" s="12"/>
+      <c r="K1" s="11"/>
+      <c r="L1" s="11"/>
+      <c r="M1" s="11"/>
+      <c r="N1" s="11"/>
+      <c r="O1" s="11"/>
+      <c r="P1" s="12"/>
+    </row>
+    <row r="2" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A2" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="C2" s="5">
-        <v>15</v>
-      </c>
-      <c r="D2" s="6">
-        <v>132000</v>
-      </c>
-      <c r="E2" s="6">
-        <v>170000</v>
-      </c>
-      <c r="F2" s="6">
-        <v>38000</v>
-      </c>
-      <c r="G2" s="6">
-        <f>F2</f>
-        <v>38000</v>
-      </c>
-      <c r="H2" s="6">
-        <f>D2+G2</f>
-        <v>170000</v>
-      </c>
-      <c r="I2" s="5" t="s">
+      <c r="B2" s="3">
+        <v>130000</v>
+      </c>
+      <c r="C2" s="3">
+        <f>SUMIFS(Анализ!W:W, Анализ!G:G, A2)</f>
+        <v>107700</v>
+      </c>
+      <c r="D2" s="3">
+        <f>MIN(C2,B2)</f>
+        <v>107700</v>
+      </c>
+      <c r="E2" s="3">
+        <f>B2-D2</f>
+        <v>22300</v>
+      </c>
+      <c r="F2" s="6"/>
+      <c r="G2" s="12"/>
+      <c r="H2" s="12"/>
+      <c r="I2" s="12"/>
+      <c r="J2" s="12"/>
+      <c r="K2" s="12"/>
+      <c r="L2" s="12"/>
+      <c r="M2" s="12"/>
+      <c r="N2" s="12"/>
+      <c r="O2" s="12"/>
+      <c r="P2" s="12"/>
+    </row>
+    <row r="3" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A3" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="B3" s="3">
+        <v>210000</v>
+      </c>
+      <c r="C3" s="3">
+        <f>SUMIFS(Анализ!W:W, Анализ!G:G, A3)</f>
+        <v>122900</v>
+      </c>
+      <c r="D3" s="3">
+        <f t="shared" ref="D3:D8" si="0">MIN(C3,B3)</f>
+        <v>122900</v>
+      </c>
+      <c r="E3" s="3">
+        <f t="shared" ref="E3:E8" si="1">B3-D3</f>
+        <v>87100</v>
+      </c>
+      <c r="F3" s="6"/>
+      <c r="G3" s="12"/>
+      <c r="H3" s="12"/>
+      <c r="I3" s="12"/>
+      <c r="J3" s="12"/>
+      <c r="K3" s="12"/>
+      <c r="L3" s="12"/>
+      <c r="M3" s="12"/>
+      <c r="N3" s="12"/>
+      <c r="O3" s="12"/>
+      <c r="P3" s="12"/>
+    </row>
+    <row r="4" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A4" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="B4" s="3">
+        <v>100000</v>
+      </c>
+      <c r="C4" s="3">
+        <f>SUMIFS(Анализ!W:W, Анализ!G:G, A4)</f>
+        <v>133400</v>
+      </c>
+      <c r="D4" s="3">
+        <f t="shared" si="0"/>
+        <v>100000</v>
+      </c>
+      <c r="E4" s="3">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="F4" s="6"/>
+      <c r="G4" s="12"/>
+      <c r="H4" s="12"/>
+      <c r="I4" s="12"/>
+      <c r="J4" s="12"/>
+      <c r="K4" s="12"/>
+      <c r="L4" s="12"/>
+      <c r="M4" s="12"/>
+      <c r="N4" s="12"/>
+      <c r="O4" s="12"/>
+      <c r="P4" s="12"/>
+    </row>
+    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A5" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="B5" s="3">
+        <v>120000</v>
+      </c>
+      <c r="C5" s="3">
+        <f>SUMIFS(Анализ!W:W, Анализ!G:G, A5)</f>
+        <v>61200</v>
+      </c>
+      <c r="D5" s="10">
+        <v>61200</v>
+      </c>
+      <c r="E5" s="3">
+        <f t="shared" si="1"/>
+        <v>58800</v>
+      </c>
+      <c r="F5" s="6"/>
+      <c r="G5" s="12"/>
+      <c r="H5" s="12"/>
+      <c r="I5" s="12"/>
+      <c r="J5" s="12"/>
+      <c r="K5" s="12"/>
+      <c r="L5" s="12"/>
+      <c r="M5" s="12"/>
+      <c r="N5" s="12"/>
+      <c r="O5" s="12"/>
+      <c r="P5" s="12"/>
+    </row>
+    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A6" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="B6" s="3">
+        <v>220000</v>
+      </c>
+      <c r="C6" s="3">
+        <f>SUMIFS(Анализ!W:W, Анализ!G:G, A6)</f>
+        <v>117600</v>
+      </c>
+      <c r="D6" s="3">
+        <f t="shared" si="0"/>
+        <v>117600</v>
+      </c>
+      <c r="E6" s="3">
+        <f t="shared" si="1"/>
+        <v>102400</v>
+      </c>
+      <c r="F6" s="6"/>
+      <c r="G6" s="12"/>
+      <c r="H6" s="12"/>
+      <c r="I6" s="12"/>
+      <c r="J6" s="12"/>
+      <c r="K6" s="12"/>
+      <c r="L6" s="12"/>
+      <c r="M6" s="12"/>
+      <c r="N6" s="12"/>
+      <c r="O6" s="12"/>
+      <c r="P6" s="12"/>
+    </row>
+    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A7" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="B7" s="3">
+        <v>80000</v>
+      </c>
+      <c r="C7" s="3">
+        <f>SUMIFS(Анализ!W:W, Анализ!G:G, A7)</f>
+        <v>47750</v>
+      </c>
+      <c r="D7" s="3">
+        <f t="shared" si="0"/>
+        <v>47750</v>
+      </c>
+      <c r="E7" s="3">
+        <f t="shared" si="1"/>
+        <v>32250</v>
+      </c>
+      <c r="F7" s="6"/>
+      <c r="G7" s="12"/>
+      <c r="H7" s="12"/>
+      <c r="I7" s="12"/>
+      <c r="J7" s="12"/>
+      <c r="K7" s="12"/>
+      <c r="L7" s="12"/>
+      <c r="M7" s="12"/>
+      <c r="N7" s="12"/>
+      <c r="O7" s="12"/>
+      <c r="P7" s="12"/>
+    </row>
+    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A8" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="B8" s="3">
+        <v>100000</v>
+      </c>
+      <c r="C8" s="3">
+        <f>SUMIFS(Анализ!W:W, Анализ!G:G, A8)</f>
+        <v>42600</v>
+      </c>
+      <c r="D8" s="3">
+        <f t="shared" si="0"/>
+        <v>42600</v>
+      </c>
+      <c r="E8" s="3">
+        <f t="shared" si="1"/>
+        <v>57400</v>
+      </c>
+      <c r="F8" s="6"/>
+      <c r="G8" s="12"/>
+      <c r="H8" s="12"/>
+      <c r="I8" s="12"/>
+      <c r="J8" s="12"/>
+      <c r="K8" s="12"/>
+      <c r="L8" s="12"/>
+      <c r="M8" s="12"/>
+      <c r="N8" s="12"/>
+      <c r="O8" s="12"/>
+      <c r="P8" s="12"/>
+    </row>
+    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A9" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="B9" s="2">
+        <f>SUM(B2:B8)</f>
+        <v>960000</v>
+      </c>
+      <c r="C9" s="2">
+        <f>SUM(C2:C8)</f>
+        <v>633150</v>
+      </c>
+      <c r="D9" s="2">
+        <f>SUM(D2:D8)</f>
+        <v>599750</v>
+      </c>
+      <c r="E9" s="2">
+        <f>SUM(E2:E8)</f>
+        <v>360250</v>
+      </c>
+      <c r="F9" s="6"/>
+      <c r="G9" s="11"/>
+      <c r="H9" s="11"/>
+      <c r="I9" s="11"/>
+      <c r="J9" s="12"/>
+      <c r="K9" s="11"/>
+      <c r="L9" s="11"/>
+      <c r="M9" s="11"/>
+      <c r="N9" s="11"/>
+      <c r="O9" s="11"/>
+      <c r="P9" s="12"/>
+    </row>
+    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="D10" s="6"/>
+      <c r="E10" s="6"/>
+      <c r="F10" s="6"/>
+      <c r="G10" s="13"/>
+      <c r="H10" s="13"/>
+      <c r="I10" s="12"/>
+      <c r="J10" s="12"/>
+      <c r="K10" s="12"/>
+      <c r="L10" s="12"/>
+      <c r="M10" s="12"/>
+      <c r="N10" s="12"/>
+      <c r="O10" s="12"/>
+      <c r="P10" s="12"/>
+    </row>
+    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A11" s="5" t="s">
+        <v>168</v>
+      </c>
+      <c r="G11" s="12"/>
+      <c r="H11" s="12"/>
+      <c r="I11" s="12"/>
+      <c r="J11" s="12"/>
+      <c r="K11" s="12"/>
+      <c r="L11" s="12"/>
+      <c r="M11" s="12"/>
+      <c r="N11" s="12"/>
+      <c r="O11" s="12"/>
+    </row>
+    <row r="12" spans="1:16" ht="17" x14ac:dyDescent="0.2">
+      <c r="A12" s="8" t="s">
+        <v>169</v>
+      </c>
+      <c r="B12" s="7" t="s">
         <v>170</v>
       </c>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A3" s="5" t="s">
-        <v>133</v>
-      </c>
-      <c r="B3" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="C3" s="5">
-        <v>15</v>
-      </c>
-      <c r="D3" s="6">
-        <v>121000</v>
-      </c>
-      <c r="E3" s="6">
-        <v>156000</v>
-      </c>
-      <c r="F3" s="6">
-        <v>35000</v>
-      </c>
-      <c r="G3" s="6">
-        <f t="shared" ref="G3:G10" si="0">F3</f>
-        <v>35000</v>
-      </c>
-      <c r="H3" s="6">
-        <f t="shared" ref="H3:H10" si="1">D3+G3</f>
-        <v>156000</v>
-      </c>
-      <c r="I3" s="5" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A4" s="5" t="s">
+      <c r="C12" s="5" t="s">
+        <v>171</v>
+      </c>
+      <c r="D12" s="5" t="s">
+        <v>172</v>
+      </c>
+      <c r="E12" s="5" t="s">
+        <v>173</v>
+      </c>
+      <c r="G12" s="14"/>
+      <c r="H12" s="11"/>
+      <c r="I12" s="11"/>
+      <c r="J12" s="11"/>
+      <c r="K12" s="11"/>
+      <c r="L12" s="12"/>
+      <c r="M12" s="12"/>
+      <c r="N12" s="12"/>
+      <c r="O12" s="12"/>
+    </row>
+    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A13" t="s">
         <v>134</v>
       </c>
-      <c r="B4" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="C4" s="5">
-        <v>15</v>
-      </c>
-      <c r="D4" s="6">
-        <v>123000</v>
-      </c>
-      <c r="E4" s="6">
-        <v>150000</v>
-      </c>
-      <c r="F4" s="6">
+      <c r="B13" s="9" t="s">
+        <v>174</v>
+      </c>
+      <c r="C13" s="4">
         <v>27000</v>
       </c>
-      <c r="G4" s="6">
-        <f t="shared" si="0"/>
+      <c r="D13" s="4">
         <v>27000</v>
       </c>
-      <c r="H4" s="6">
-        <f t="shared" si="1"/>
-        <v>150000</v>
-      </c>
-      <c r="I4" s="5" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A5" s="5" t="s">
-        <v>135</v>
-      </c>
-      <c r="B5" s="5" t="s">
-        <v>80</v>
-      </c>
-      <c r="C5" s="5">
-        <v>15</v>
-      </c>
-      <c r="D5" s="6">
-        <v>113000</v>
-      </c>
-      <c r="E5" s="6">
-        <v>143000</v>
-      </c>
-      <c r="F5" s="6">
-        <v>30000</v>
-      </c>
-      <c r="G5" s="6">
-        <f t="shared" si="0"/>
-        <v>30000</v>
-      </c>
-      <c r="H5" s="6">
-        <f t="shared" si="1"/>
-        <v>143000</v>
-      </c>
-      <c r="I5" s="5" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A6" s="5" t="s">
-        <v>136</v>
-      </c>
-      <c r="B6" s="5" t="s">
-        <v>97</v>
-      </c>
-      <c r="C6" s="5">
-        <v>15</v>
-      </c>
-      <c r="D6" s="6">
-        <v>108000</v>
-      </c>
-      <c r="E6" s="6">
-        <v>136000</v>
-      </c>
-      <c r="F6" s="6">
-        <v>28000</v>
-      </c>
-      <c r="G6" s="6">
-        <f t="shared" si="0"/>
-        <v>28000</v>
-      </c>
-      <c r="H6" s="6">
-        <f t="shared" si="1"/>
-        <v>136000</v>
-      </c>
-      <c r="I6" s="5" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A7" s="5" t="s">
-        <v>137</v>
-      </c>
-      <c r="B7" s="5" t="s">
-        <v>107</v>
-      </c>
-      <c r="C7" s="5">
-        <v>14</v>
-      </c>
-      <c r="D7" s="6">
-        <v>99000</v>
-      </c>
-      <c r="E7" s="6">
-        <v>116000</v>
-      </c>
-      <c r="F7" s="6">
-        <v>17000</v>
-      </c>
-      <c r="G7" s="6">
-        <f t="shared" si="0"/>
-        <v>17000</v>
-      </c>
-      <c r="H7" s="6">
-        <f t="shared" si="1"/>
-        <v>116000</v>
-      </c>
-      <c r="I7" s="5" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A8" s="5" t="s">
-        <v>138</v>
-      </c>
-      <c r="B8" s="5" t="s">
-        <v>123</v>
-      </c>
-      <c r="C8" s="5">
-        <v>13</v>
-      </c>
-      <c r="D8" s="6">
-        <v>75000</v>
-      </c>
-      <c r="E8" s="6">
-        <v>98000</v>
-      </c>
-      <c r="F8" s="6">
-        <v>23000</v>
-      </c>
-      <c r="G8" s="6">
-        <f t="shared" si="0"/>
-        <v>23000</v>
-      </c>
-      <c r="H8" s="6">
-        <f t="shared" si="1"/>
-        <v>98000</v>
-      </c>
-      <c r="I8" s="5" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A9" s="5" t="s">
-        <v>139</v>
-      </c>
-      <c r="B9" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="C9" s="5">
-        <v>15</v>
-      </c>
-      <c r="D9" s="6">
-        <v>128000</v>
-      </c>
-      <c r="E9" s="6">
-        <v>156000</v>
-      </c>
-      <c r="F9" s="6">
-        <v>28000</v>
-      </c>
-      <c r="G9" s="6">
-        <f t="shared" si="0"/>
-        <v>28000</v>
-      </c>
-      <c r="H9" s="6">
-        <f t="shared" si="1"/>
-        <v>156000</v>
-      </c>
-      <c r="I9" s="5" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A10" s="5" t="s">
-        <v>146</v>
-      </c>
-      <c r="B10" s="5" t="s">
-        <v>97</v>
-      </c>
-      <c r="C10" s="5">
-        <v>15</v>
-      </c>
-      <c r="D10" s="6">
-        <v>92000</v>
-      </c>
-      <c r="E10" s="6">
-        <v>136000</v>
-      </c>
-      <c r="F10" s="6">
-        <v>44000</v>
-      </c>
-      <c r="G10" s="6">
-        <f t="shared" si="0"/>
-        <v>44000</v>
-      </c>
-      <c r="H10" s="6">
-        <f t="shared" si="1"/>
-        <v>136000</v>
-      </c>
-      <c r="I10" s="5" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9" ht="17" x14ac:dyDescent="0.2">
-      <c r="A12" s="2" t="s">
-        <v>172</v>
-      </c>
-      <c r="B12" s="7">
-        <f>SUM(G2:G10)</f>
-        <v>270000</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A13" t="s">
-        <v>173</v>
-      </c>
-      <c r="B13" s="7">
-        <f>SUM(G19:G65)</f>
-        <v>496000</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="E13" t="s">
+        <v>176</v>
+      </c>
+      <c r="G13" s="12"/>
+      <c r="H13" s="15"/>
+      <c r="I13" s="15"/>
+      <c r="J13" s="12"/>
+      <c r="K13" s="12"/>
+      <c r="L13" s="12"/>
+      <c r="M13" s="12"/>
+      <c r="N13" s="12"/>
+      <c r="O13" s="12"/>
+    </row>
+    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>167</v>
-      </c>
-      <c r="B14" s="7">
-        <f>B12+B13</f>
-        <v>766000</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A15" s="3" t="s">
-        <v>168</v>
-      </c>
-      <c r="B15" s="8">
-        <v>960000</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A16" s="3" t="s">
-        <v>169</v>
-      </c>
-      <c r="B16" s="8">
-        <f>B15-B14</f>
-        <v>194000</v>
-      </c>
-    </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="B17" s="7"/>
-    </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A18" s="4" t="s">
-        <v>158</v>
+        <v>67</v>
+      </c>
+      <c r="B14" s="9" t="s">
+        <v>175</v>
+      </c>
+      <c r="C14" s="4">
+        <v>24000</v>
+      </c>
+      <c r="D14" s="4">
+        <v>24000</v>
+      </c>
+      <c r="E14" t="s">
+        <v>176</v>
+      </c>
+      <c r="G14" s="12"/>
+      <c r="H14" s="15"/>
+      <c r="I14" s="15"/>
+      <c r="J14" s="12"/>
+      <c r="K14" s="12"/>
+      <c r="L14" s="12"/>
+      <c r="M14" s="12"/>
+      <c r="N14" s="12"/>
+      <c r="O14" s="12"/>
+    </row>
+    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A15" t="s">
+        <v>64</v>
+      </c>
+      <c r="B15" s="9" t="s">
+        <v>175</v>
+      </c>
+      <c r="C15" s="4">
+        <v>22000</v>
+      </c>
+      <c r="D15" s="4">
+        <v>22000</v>
+      </c>
+      <c r="E15" t="s">
+        <v>176</v>
+      </c>
+      <c r="G15" s="12"/>
+      <c r="H15" s="15"/>
+      <c r="I15" s="15"/>
+      <c r="J15" s="12"/>
+      <c r="K15" s="12"/>
+      <c r="L15" s="12"/>
+      <c r="M15" s="12"/>
+      <c r="N15" s="12"/>
+      <c r="O15" s="12"/>
+    </row>
+    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A16" t="s">
+        <v>70</v>
+      </c>
+      <c r="B16" s="9" t="s">
+        <v>175</v>
+      </c>
+      <c r="C16" s="4">
+        <v>16000</v>
+      </c>
+      <c r="D16" s="4">
+        <v>16000</v>
+      </c>
+      <c r="E16" t="s">
+        <v>176</v>
+      </c>
+      <c r="G16" s="12"/>
+      <c r="H16" s="15"/>
+      <c r="I16" s="15"/>
+      <c r="J16" s="12"/>
+      <c r="K16" s="12"/>
+      <c r="L16" s="12"/>
+      <c r="M16" s="12"/>
+      <c r="N16" s="12"/>
+      <c r="O16" s="12"/>
+    </row>
+    <row r="17" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A17" t="s">
+        <v>75</v>
+      </c>
+      <c r="B17" s="9" t="s">
+        <v>175</v>
+      </c>
+      <c r="C17" s="4">
+        <v>12000</v>
+      </c>
+      <c r="D17" s="4">
+        <v>11000</v>
+      </c>
+      <c r="E17" t="s">
+        <v>177</v>
+      </c>
+      <c r="G17" s="12"/>
+      <c r="H17" s="15"/>
+      <c r="I17" s="15"/>
+      <c r="J17" s="12"/>
+      <c r="K17" s="12"/>
+      <c r="L17" s="12"/>
+      <c r="M17" s="12"/>
+      <c r="N17" s="12"/>
+      <c r="O17" s="12"/>
+    </row>
+    <row r="18" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A18" t="s">
+        <v>60</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>159</v>
-      </c>
-      <c r="C18" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D18" s="4" t="s">
-        <v>157</v>
+        <v>175</v>
+      </c>
+      <c r="C18" s="4">
+        <v>8000</v>
+      </c>
+      <c r="D18" s="4">
+        <v>0</v>
       </c>
       <c r="E18" s="4" t="s">
-        <v>153</v>
-      </c>
-      <c r="F18" s="4" t="s">
-        <v>165</v>
-      </c>
-      <c r="G18" s="4" t="s">
-        <v>161</v>
-      </c>
-      <c r="H18" s="4" t="s">
-        <v>162</v>
-      </c>
-      <c r="I18" s="4" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A19" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="B19" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="C19" s="5">
-        <v>13</v>
-      </c>
-      <c r="D19" s="6">
-        <v>165000</v>
-      </c>
-      <c r="E19" s="6">
-        <v>180000</v>
-      </c>
-      <c r="F19" s="6">
-        <v>15000</v>
-      </c>
-      <c r="G19" s="6">
-        <f>F19</f>
-        <v>15000</v>
-      </c>
-      <c r="H19" s="6">
-        <f>D19+G19</f>
-        <v>180000</v>
-      </c>
-      <c r="I19" s="5" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A20" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="B20" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="C20" s="5">
-        <v>13</v>
-      </c>
-      <c r="D20" s="6">
-        <v>165000</v>
-      </c>
-      <c r="E20" s="6">
-        <v>180000</v>
-      </c>
-      <c r="F20" s="6">
-        <v>15000</v>
-      </c>
-      <c r="G20" s="6">
-        <f t="shared" ref="G20:G65" si="2">F20</f>
-        <v>15000</v>
-      </c>
-      <c r="H20" s="6">
-        <f t="shared" ref="H20:H65" si="3">D20+G20</f>
-        <v>180000</v>
-      </c>
-      <c r="I20" s="5" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A21" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="B21" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="C21" s="5">
-        <v>14</v>
-      </c>
-      <c r="D21" s="6">
-        <v>174000</v>
-      </c>
-      <c r="E21" s="6">
-        <v>190000</v>
-      </c>
-      <c r="F21" s="6">
-        <v>16000</v>
-      </c>
-      <c r="G21" s="6">
-        <f t="shared" si="2"/>
-        <v>16000</v>
-      </c>
-      <c r="H21" s="6">
-        <f t="shared" si="3"/>
-        <v>190000</v>
-      </c>
-      <c r="I21" s="5" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A22" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="B22" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="C22" s="5">
-        <v>16</v>
-      </c>
-      <c r="D22" s="6">
-        <v>209000</v>
-      </c>
-      <c r="E22" s="6">
-        <v>210000</v>
-      </c>
-      <c r="F22" s="6">
-        <v>1000</v>
-      </c>
-      <c r="G22" s="6">
-        <f t="shared" si="2"/>
-        <v>1000</v>
-      </c>
-      <c r="H22" s="6">
-        <f t="shared" si="3"/>
-        <v>210000</v>
-      </c>
-      <c r="I22" s="5" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A23" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="B23" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="C23" s="5">
-        <v>15</v>
-      </c>
-      <c r="D23" s="6">
-        <v>188000</v>
-      </c>
-      <c r="E23" s="6">
-        <v>200000</v>
-      </c>
-      <c r="F23" s="6">
-        <v>12000</v>
-      </c>
-      <c r="G23" s="6">
-        <f t="shared" si="2"/>
-        <v>12000</v>
-      </c>
-      <c r="H23" s="6">
-        <f t="shared" si="3"/>
-        <v>200000</v>
-      </c>
-      <c r="I23" s="5" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A24" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="B24" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="C24" s="5">
-        <v>16</v>
-      </c>
-      <c r="D24" s="6">
-        <v>195000</v>
-      </c>
-      <c r="E24" s="6">
-        <v>210000</v>
-      </c>
-      <c r="F24" s="6">
-        <v>15000</v>
-      </c>
-      <c r="G24" s="6">
-        <f t="shared" si="2"/>
-        <v>15000</v>
-      </c>
-      <c r="H24" s="6">
-        <f t="shared" si="3"/>
-        <v>210000</v>
-      </c>
-      <c r="I24" s="5" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A25" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="B25" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="C25" s="5">
-        <v>16</v>
-      </c>
-      <c r="D25" s="6">
-        <v>203000</v>
-      </c>
-      <c r="E25" s="6">
-        <v>210000</v>
-      </c>
-      <c r="F25" s="6">
+        <v>178</v>
+      </c>
+      <c r="F18" s="5"/>
+      <c r="G18" s="12"/>
+      <c r="H18" s="15"/>
+      <c r="I18" s="15"/>
+      <c r="J18" s="15"/>
+      <c r="K18" s="15"/>
+      <c r="L18" s="12"/>
+      <c r="M18" s="12"/>
+      <c r="N18" s="12"/>
+      <c r="O18" s="12"/>
+    </row>
+    <row r="19" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A19" t="s">
+        <v>71</v>
+      </c>
+      <c r="B19" s="4" t="s">
+        <v>175</v>
+      </c>
+      <c r="C19" s="4">
+        <v>7200</v>
+      </c>
+      <c r="D19" s="9">
+        <v>0</v>
+      </c>
+      <c r="E19" s="4" t="s">
+        <v>178</v>
+      </c>
+      <c r="F19" s="6"/>
+      <c r="G19" s="12"/>
+      <c r="H19" s="15"/>
+      <c r="I19" s="16"/>
+      <c r="J19" s="15"/>
+      <c r="K19" s="15"/>
+      <c r="L19" s="12"/>
+      <c r="M19" s="12"/>
+      <c r="N19" s="12"/>
+      <c r="O19" s="12"/>
+    </row>
+    <row r="20" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A20" t="s">
+        <v>74</v>
+      </c>
+      <c r="B20" s="4" t="s">
+        <v>175</v>
+      </c>
+      <c r="C20" s="4">
+        <v>7200</v>
+      </c>
+      <c r="D20" s="9">
+        <v>0</v>
+      </c>
+      <c r="E20" s="4" t="s">
+        <v>178</v>
+      </c>
+      <c r="F20" s="6"/>
+      <c r="G20" s="12"/>
+      <c r="H20" s="15"/>
+      <c r="I20" s="16"/>
+      <c r="J20" s="15"/>
+      <c r="K20" s="15"/>
+      <c r="L20" s="12"/>
+      <c r="M20" s="12"/>
+      <c r="N20" s="12"/>
+      <c r="O20" s="12"/>
+    </row>
+    <row r="21" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A21" t="s">
+        <v>72</v>
+      </c>
+      <c r="B21" s="4" t="s">
+        <v>175</v>
+      </c>
+      <c r="C21" s="4">
         <v>7000</v>
       </c>
-      <c r="G25" s="6">
-        <f t="shared" si="2"/>
-        <v>7000</v>
-      </c>
-      <c r="H25" s="6">
-        <f t="shared" si="3"/>
-        <v>210000</v>
-      </c>
-      <c r="I25" s="5" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A26" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B26" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="C26" s="5">
-        <v>18</v>
-      </c>
-      <c r="D26" s="6">
-        <v>228000</v>
-      </c>
-      <c r="E26" s="6">
-        <v>230000</v>
-      </c>
-      <c r="F26" s="6">
-        <v>2000</v>
-      </c>
-      <c r="G26" s="6">
-        <f t="shared" si="2"/>
-        <v>2000</v>
-      </c>
-      <c r="H26" s="6">
-        <f t="shared" si="3"/>
-        <v>230000</v>
-      </c>
-      <c r="I26" s="5" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A27" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B27" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="C27" s="5">
-        <v>13</v>
-      </c>
-      <c r="D27" s="6">
-        <v>163000</v>
-      </c>
-      <c r="E27" s="6">
-        <v>166000</v>
-      </c>
-      <c r="F27" s="6">
+      <c r="D21" s="9">
+        <v>0</v>
+      </c>
+      <c r="E21" s="4" t="s">
+        <v>178</v>
+      </c>
+      <c r="F21" s="6"/>
+      <c r="G21" s="12"/>
+      <c r="H21" s="15"/>
+      <c r="I21" s="16"/>
+      <c r="J21" s="15"/>
+      <c r="K21" s="15"/>
+      <c r="L21" s="12"/>
+      <c r="M21" s="12"/>
+      <c r="N21" s="12"/>
+      <c r="O21" s="12"/>
+    </row>
+    <row r="22" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A22" t="s">
+        <v>62</v>
+      </c>
+      <c r="B22" t="s">
+        <v>175</v>
+      </c>
+      <c r="C22" s="4">
         <v>3000</v>
       </c>
-      <c r="G27" s="6">
-        <f t="shared" si="2"/>
-        <v>3000</v>
-      </c>
-      <c r="H27" s="6">
-        <f t="shared" si="3"/>
-        <v>166000</v>
-      </c>
-      <c r="I27" s="5" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A28" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="B28" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="C28" s="5">
-        <v>13</v>
-      </c>
-      <c r="D28" s="6">
-        <v>146000</v>
-      </c>
-      <c r="E28" s="6">
-        <v>166000</v>
-      </c>
-      <c r="F28" s="6">
-        <v>20000</v>
-      </c>
-      <c r="G28" s="6">
-        <f t="shared" si="2"/>
-        <v>20000</v>
-      </c>
-      <c r="H28" s="6">
-        <f t="shared" si="3"/>
-        <v>166000</v>
-      </c>
-      <c r="I28" s="5" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A29" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="B29" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="C29" s="5">
-        <v>14</v>
-      </c>
-      <c r="D29" s="6">
-        <v>161000</v>
-      </c>
-      <c r="E29" s="6">
-        <v>175000</v>
-      </c>
-      <c r="F29" s="6">
-        <v>14000</v>
-      </c>
-      <c r="G29" s="6">
-        <f t="shared" si="2"/>
-        <v>14000</v>
-      </c>
-      <c r="H29" s="6">
-        <f t="shared" si="3"/>
-        <v>175000</v>
-      </c>
-      <c r="I29" s="5" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A30" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="B30" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="C30" s="5">
-        <v>16</v>
-      </c>
-      <c r="D30" s="6">
-        <v>176000</v>
-      </c>
-      <c r="E30" s="6">
-        <v>193000</v>
-      </c>
-      <c r="F30" s="6">
-        <v>17000</v>
-      </c>
-      <c r="G30" s="6">
-        <f t="shared" si="2"/>
-        <v>17000</v>
-      </c>
-      <c r="H30" s="6">
-        <f t="shared" si="3"/>
-        <v>193000</v>
-      </c>
-      <c r="I30" s="5" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A31" s="5" t="s">
-        <v>56</v>
-      </c>
-      <c r="B31" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="C31" s="5">
-        <v>17</v>
-      </c>
-      <c r="D31" s="6">
-        <v>178000</v>
-      </c>
-      <c r="E31" s="6">
-        <v>202000</v>
-      </c>
-      <c r="F31" s="6">
-        <v>24000</v>
-      </c>
-      <c r="G31" s="6">
-        <f t="shared" si="2"/>
-        <v>24000</v>
-      </c>
-      <c r="H31" s="6">
-        <f t="shared" si="3"/>
-        <v>202000</v>
-      </c>
-      <c r="I31" s="5" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A32" s="5" t="s">
-        <v>58</v>
-      </c>
-      <c r="B32" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="C32" s="5">
-        <v>17</v>
-      </c>
-      <c r="D32" s="6">
-        <v>187000</v>
-      </c>
-      <c r="E32" s="6">
-        <v>202000</v>
-      </c>
-      <c r="F32" s="6">
-        <v>15000</v>
-      </c>
-      <c r="G32" s="6">
-        <f t="shared" si="2"/>
-        <v>15000</v>
-      </c>
-      <c r="H32" s="6">
-        <f t="shared" si="3"/>
-        <v>202000</v>
-      </c>
-      <c r="I32" s="5" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A33" s="5" t="s">
-        <v>59</v>
-      </c>
-      <c r="B33" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="C33" s="5">
-        <v>17</v>
-      </c>
-      <c r="D33" s="6">
-        <v>200000</v>
-      </c>
-      <c r="E33" s="6">
-        <v>202000</v>
-      </c>
-      <c r="F33" s="6">
-        <v>2000</v>
-      </c>
-      <c r="G33" s="6">
-        <f t="shared" si="2"/>
-        <v>2000</v>
-      </c>
-      <c r="H33" s="6">
-        <f t="shared" si="3"/>
-        <v>202000</v>
-      </c>
-      <c r="I33" s="5" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A34" s="5" t="s">
-        <v>60</v>
-      </c>
-      <c r="B34" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="C34" s="5">
-        <v>13</v>
-      </c>
-      <c r="D34" s="6">
-        <v>142000</v>
-      </c>
-      <c r="E34" s="6">
-        <v>158000</v>
-      </c>
-      <c r="F34" s="6">
-        <v>16000</v>
-      </c>
-      <c r="G34" s="6">
-        <f t="shared" si="2"/>
-        <v>16000</v>
-      </c>
-      <c r="H34" s="6">
-        <f t="shared" si="3"/>
-        <v>158000</v>
-      </c>
-      <c r="I34" s="5" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A35" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="B35" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="C35" s="5">
-        <v>13</v>
-      </c>
-      <c r="D35" s="6">
-        <v>152000</v>
-      </c>
-      <c r="E35" s="6">
-        <v>158000</v>
-      </c>
-      <c r="F35" s="6">
-        <v>6000</v>
-      </c>
-      <c r="G35" s="6">
-        <f t="shared" si="2"/>
-        <v>6000</v>
-      </c>
-      <c r="H35" s="6">
-        <f t="shared" si="3"/>
-        <v>158000</v>
-      </c>
-      <c r="I35" s="5" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A36" s="5" t="s">
-        <v>64</v>
-      </c>
-      <c r="B36" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="C36" s="5">
-        <v>14</v>
-      </c>
-      <c r="D36" s="6">
-        <v>145000</v>
-      </c>
-      <c r="E36" s="6">
-        <v>167000</v>
-      </c>
-      <c r="F36" s="6">
-        <v>22000</v>
-      </c>
-      <c r="G36" s="6">
-        <f t="shared" si="2"/>
-        <v>22000</v>
-      </c>
-      <c r="H36" s="6">
-        <f t="shared" si="3"/>
-        <v>167000</v>
-      </c>
-      <c r="I36" s="5" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A37" s="5" t="s">
-        <v>67</v>
-      </c>
-      <c r="B37" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="C37" s="5">
-        <v>15</v>
-      </c>
-      <c r="D37" s="6">
-        <v>152000</v>
-      </c>
-      <c r="E37" s="6">
-        <v>176000</v>
-      </c>
-      <c r="F37" s="6">
-        <v>24000</v>
-      </c>
-      <c r="G37" s="6">
-        <f t="shared" si="2"/>
-        <v>24000</v>
-      </c>
-      <c r="H37" s="6">
-        <f t="shared" si="3"/>
-        <v>176000</v>
-      </c>
-      <c r="I37" s="5" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A38" s="5" t="s">
-        <v>70</v>
-      </c>
-      <c r="B38" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="C38" s="5">
-        <v>16</v>
-      </c>
-      <c r="D38" s="6">
-        <v>169000</v>
-      </c>
-      <c r="E38" s="6">
-        <v>185000</v>
-      </c>
-      <c r="F38" s="6">
-        <v>16000</v>
-      </c>
-      <c r="G38" s="6">
-        <f t="shared" si="2"/>
-        <v>16000</v>
-      </c>
-      <c r="H38" s="6">
-        <f t="shared" si="3"/>
-        <v>185000</v>
-      </c>
-      <c r="I38" s="5" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A39" s="5" t="s">
-        <v>71</v>
-      </c>
-      <c r="B39" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="C39" s="5">
-        <v>16</v>
-      </c>
-      <c r="D39" s="6">
-        <v>173000</v>
-      </c>
-      <c r="E39" s="6">
-        <v>185000</v>
-      </c>
-      <c r="F39" s="6">
-        <v>12000</v>
-      </c>
-      <c r="G39" s="6">
-        <f t="shared" si="2"/>
-        <v>12000</v>
-      </c>
-      <c r="H39" s="6">
-        <f t="shared" si="3"/>
-        <v>185000</v>
-      </c>
-      <c r="I39" s="5" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A40" s="5" t="s">
-        <v>72</v>
-      </c>
-      <c r="B40" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="C40" s="5">
-        <v>17</v>
-      </c>
-      <c r="D40" s="6">
-        <v>180000</v>
-      </c>
-      <c r="E40" s="6">
-        <v>194000</v>
-      </c>
-      <c r="F40" s="6">
-        <v>14000</v>
-      </c>
-      <c r="G40" s="6">
-        <f t="shared" si="2"/>
-        <v>14000</v>
-      </c>
-      <c r="H40" s="6">
-        <f t="shared" si="3"/>
-        <v>194000</v>
-      </c>
-      <c r="I40" s="5" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A41" s="5" t="s">
-        <v>74</v>
-      </c>
-      <c r="B41" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="C41" s="5">
-        <v>17</v>
-      </c>
-      <c r="D41" s="6">
-        <v>170000</v>
-      </c>
-      <c r="E41" s="6">
-        <v>194000</v>
-      </c>
-      <c r="F41" s="6">
-        <v>24000</v>
-      </c>
-      <c r="G41" s="6">
-        <f t="shared" si="2"/>
-        <v>24000</v>
-      </c>
-      <c r="H41" s="6">
-        <f t="shared" si="3"/>
-        <v>194000</v>
-      </c>
-      <c r="I41" s="5" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="42" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A42" s="5" t="s">
-        <v>75</v>
-      </c>
-      <c r="B42" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="C42" s="5">
-        <v>18</v>
-      </c>
-      <c r="D42" s="6">
-        <v>182000</v>
-      </c>
-      <c r="E42" s="6">
-        <v>202000</v>
-      </c>
-      <c r="F42" s="6">
-        <v>20000</v>
-      </c>
-      <c r="G42" s="6">
-        <f t="shared" si="2"/>
-        <v>20000</v>
-      </c>
-      <c r="H42" s="6">
-        <f t="shared" si="3"/>
-        <v>202000</v>
-      </c>
-      <c r="I42" s="5" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="43" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A43" s="5" t="s">
-        <v>77</v>
-      </c>
-      <c r="B43" s="5" t="s">
-        <v>80</v>
-      </c>
-      <c r="C43" s="5">
-        <v>13</v>
-      </c>
-      <c r="D43" s="6">
-        <v>142000</v>
-      </c>
-      <c r="E43" s="6">
-        <v>151000</v>
-      </c>
-      <c r="F43" s="6">
-        <v>9000</v>
-      </c>
-      <c r="G43" s="6">
-        <f t="shared" si="2"/>
-        <v>9000</v>
-      </c>
-      <c r="H43" s="6">
-        <f t="shared" si="3"/>
-        <v>151000</v>
-      </c>
-      <c r="I43" s="5" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="44" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A44" s="5" t="s">
-        <v>81</v>
-      </c>
-      <c r="B44" s="5" t="s">
-        <v>80</v>
-      </c>
-      <c r="C44" s="5">
-        <v>13</v>
-      </c>
-      <c r="D44" s="6">
-        <v>144000</v>
-      </c>
-      <c r="E44" s="6">
-        <v>151000</v>
-      </c>
-      <c r="F44" s="6">
-        <v>7000</v>
-      </c>
-      <c r="G44" s="6">
-        <f t="shared" si="2"/>
-        <v>7000</v>
-      </c>
-      <c r="H44" s="6">
-        <f t="shared" si="3"/>
-        <v>151000</v>
-      </c>
-      <c r="I44" s="5" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="45" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A45" s="5" t="s">
-        <v>86</v>
-      </c>
-      <c r="B45" s="5" t="s">
-        <v>80</v>
-      </c>
-      <c r="C45" s="5">
-        <v>14</v>
-      </c>
-      <c r="D45" s="6">
-        <v>153000</v>
-      </c>
-      <c r="E45" s="6">
-        <v>160000</v>
-      </c>
-      <c r="F45" s="6">
-        <v>7000</v>
-      </c>
-      <c r="G45" s="6">
-        <f t="shared" si="2"/>
-        <v>7000</v>
-      </c>
-      <c r="H45" s="6">
-        <f t="shared" si="3"/>
-        <v>160000</v>
-      </c>
-      <c r="I45" s="5" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="46" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A46" s="5" t="s">
-        <v>89</v>
-      </c>
-      <c r="B46" s="5" t="s">
-        <v>80</v>
-      </c>
-      <c r="C46" s="5">
-        <v>16</v>
-      </c>
-      <c r="D46" s="6">
-        <v>173000</v>
-      </c>
-      <c r="E46" s="6">
-        <v>176000</v>
-      </c>
-      <c r="F46" s="6">
-        <v>3000</v>
-      </c>
-      <c r="G46" s="6">
-        <f t="shared" si="2"/>
-        <v>3000</v>
-      </c>
-      <c r="H46" s="6">
-        <f t="shared" si="3"/>
-        <v>176000</v>
-      </c>
-      <c r="I46" s="5" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="47" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A47" s="5" t="s">
-        <v>92</v>
-      </c>
-      <c r="B47" s="5" t="s">
-        <v>80</v>
-      </c>
-      <c r="C47" s="5">
-        <v>17</v>
-      </c>
-      <c r="D47" s="6">
-        <v>174000</v>
-      </c>
-      <c r="E47" s="6">
-        <v>185000</v>
-      </c>
-      <c r="F47" s="6">
-        <v>11000</v>
-      </c>
-      <c r="G47" s="6">
-        <f t="shared" si="2"/>
-        <v>11000</v>
-      </c>
-      <c r="H47" s="6">
-        <f t="shared" si="3"/>
-        <v>185000</v>
-      </c>
-      <c r="I47" s="5" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="48" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A48" s="5" t="s">
-        <v>96</v>
-      </c>
-      <c r="B48" s="5" t="s">
-        <v>97</v>
-      </c>
-      <c r="C48" s="5">
-        <v>14</v>
-      </c>
-      <c r="D48" s="6">
-        <v>140000</v>
-      </c>
-      <c r="E48" s="6">
-        <v>152000</v>
-      </c>
-      <c r="F48" s="6">
-        <v>12000</v>
-      </c>
-      <c r="G48" s="6">
-        <f t="shared" si="2"/>
-        <v>12000</v>
-      </c>
-      <c r="H48" s="6">
-        <f t="shared" si="3"/>
-        <v>152000</v>
-      </c>
-      <c r="I48" s="5" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="49" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A49" s="5" t="s">
-        <v>98</v>
-      </c>
-      <c r="B49" s="5" t="s">
-        <v>97</v>
-      </c>
-      <c r="C49" s="5">
-        <v>14</v>
-      </c>
-      <c r="D49" s="6">
-        <v>138000</v>
-      </c>
-      <c r="E49" s="6">
-        <v>152000</v>
-      </c>
-      <c r="F49" s="6">
-        <v>14000</v>
-      </c>
-      <c r="G49" s="6">
-        <f t="shared" si="2"/>
-        <v>14000</v>
-      </c>
-      <c r="H49" s="6">
-        <f t="shared" si="3"/>
-        <v>152000</v>
-      </c>
-      <c r="I49" s="5" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="50" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A50" s="5" t="s">
-        <v>100</v>
-      </c>
-      <c r="B50" s="5" t="s">
-        <v>97</v>
-      </c>
-      <c r="C50" s="5">
-        <v>15</v>
-      </c>
-      <c r="D50" s="6">
-        <v>148000</v>
-      </c>
-      <c r="E50" s="6">
-        <v>160000</v>
-      </c>
-      <c r="F50" s="6">
-        <v>12000</v>
-      </c>
-      <c r="G50" s="6">
-        <f t="shared" si="2"/>
-        <v>12000</v>
-      </c>
-      <c r="H50" s="6">
-        <f t="shared" si="3"/>
-        <v>160000</v>
-      </c>
-      <c r="I50" s="5" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="51" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A51" s="5" t="s">
-        <v>68</v>
-      </c>
-      <c r="B51" s="5" t="s">
-        <v>97</v>
-      </c>
-      <c r="C51" s="5">
-        <v>15</v>
-      </c>
-      <c r="D51" s="6">
-        <v>158000</v>
-      </c>
-      <c r="E51" s="6">
-        <v>160000</v>
-      </c>
-      <c r="F51" s="6">
-        <v>2000</v>
-      </c>
-      <c r="G51" s="6">
-        <f t="shared" si="2"/>
-        <v>2000</v>
-      </c>
-      <c r="H51" s="6">
-        <f t="shared" si="3"/>
-        <v>160000</v>
-      </c>
-      <c r="I51" s="5" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="52" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A52" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="B52" s="5" t="s">
-        <v>97</v>
-      </c>
-      <c r="C52" s="5">
-        <v>16</v>
-      </c>
-      <c r="D52" s="6">
-        <v>150000</v>
-      </c>
-      <c r="E52" s="6">
-        <v>168000</v>
-      </c>
-      <c r="F52" s="6">
-        <v>18000</v>
-      </c>
-      <c r="G52" s="6">
-        <f t="shared" si="2"/>
-        <v>18000</v>
-      </c>
-      <c r="H52" s="6">
-        <f t="shared" si="3"/>
-        <v>168000</v>
-      </c>
-      <c r="I52" s="5" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="53" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A53" s="5" t="s">
-        <v>75</v>
-      </c>
-      <c r="B53" s="5" t="s">
-        <v>97</v>
-      </c>
-      <c r="C53" s="5">
-        <v>16</v>
-      </c>
-      <c r="D53" s="6">
-        <v>163000</v>
-      </c>
-      <c r="E53" s="6">
-        <v>168000</v>
-      </c>
-      <c r="F53" s="6">
-        <v>5000</v>
-      </c>
-      <c r="G53" s="6">
-        <f t="shared" si="2"/>
-        <v>5000</v>
-      </c>
-      <c r="H53" s="6">
-        <f t="shared" si="3"/>
-        <v>168000</v>
-      </c>
-      <c r="I53" s="5" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="54" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A54" s="5" t="s">
-        <v>85</v>
-      </c>
-      <c r="B54" s="5" t="s">
-        <v>97</v>
-      </c>
-      <c r="C54" s="5">
-        <v>17</v>
-      </c>
-      <c r="D54" s="6">
-        <v>175000</v>
-      </c>
-      <c r="E54" s="6">
-        <v>176000</v>
-      </c>
-      <c r="F54" s="6">
-        <v>1000</v>
-      </c>
-      <c r="G54" s="6">
-        <f t="shared" si="2"/>
-        <v>1000</v>
-      </c>
-      <c r="H54" s="6">
-        <f t="shared" si="3"/>
-        <v>176000</v>
-      </c>
-      <c r="I54" s="5" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="55" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A55" s="5" t="s">
-        <v>109</v>
-      </c>
-      <c r="B55" s="5" t="s">
-        <v>107</v>
-      </c>
-      <c r="C55" s="5">
-        <v>12</v>
-      </c>
-      <c r="D55" s="6">
-        <v>121000</v>
-      </c>
-      <c r="E55" s="6">
-        <v>122000</v>
-      </c>
-      <c r="F55" s="6">
-        <v>1000</v>
-      </c>
-      <c r="G55" s="6">
-        <f t="shared" si="2"/>
-        <v>1000</v>
-      </c>
-      <c r="H55" s="6">
-        <f t="shared" si="3"/>
-        <v>122000</v>
-      </c>
-      <c r="I55" s="5" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="56" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A56" s="5" t="s">
-        <v>110</v>
-      </c>
-      <c r="B56" s="5" t="s">
-        <v>107</v>
-      </c>
-      <c r="C56" s="5">
-        <v>12</v>
-      </c>
-      <c r="D56" s="6">
-        <v>116000</v>
-      </c>
-      <c r="E56" s="6">
-        <v>122000</v>
-      </c>
-      <c r="F56" s="6">
-        <v>6000</v>
-      </c>
-      <c r="G56" s="6">
-        <f t="shared" si="2"/>
-        <v>6000</v>
-      </c>
-      <c r="H56" s="6">
-        <f t="shared" si="3"/>
-        <v>122000</v>
-      </c>
-      <c r="I56" s="5" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="57" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A57" s="5" t="s">
-        <v>113</v>
-      </c>
-      <c r="B57" s="5" t="s">
-        <v>107</v>
-      </c>
-      <c r="C57" s="5">
-        <v>13</v>
-      </c>
-      <c r="D57" s="6">
-        <v>129000</v>
-      </c>
-      <c r="E57" s="6">
-        <v>130000</v>
-      </c>
-      <c r="F57" s="6">
-        <v>1000</v>
-      </c>
-      <c r="G57" s="6">
-        <f t="shared" si="2"/>
-        <v>1000</v>
-      </c>
-      <c r="H57" s="6">
-        <f t="shared" si="3"/>
-        <v>130000</v>
-      </c>
-      <c r="I57" s="5" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="58" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A58" s="5" t="s">
-        <v>117</v>
-      </c>
-      <c r="B58" s="5" t="s">
-        <v>107</v>
-      </c>
-      <c r="C58" s="5">
-        <v>15</v>
-      </c>
-      <c r="D58" s="6">
-        <v>141000</v>
-      </c>
-      <c r="E58" s="6">
-        <v>144000</v>
-      </c>
-      <c r="F58" s="6">
-        <v>3000</v>
-      </c>
-      <c r="G58" s="6">
-        <f t="shared" si="2"/>
-        <v>3000</v>
-      </c>
-      <c r="H58" s="6">
-        <f t="shared" si="3"/>
-        <v>144000</v>
-      </c>
-      <c r="I58" s="5" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="59" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A59" s="5" t="s">
-        <v>118</v>
-      </c>
-      <c r="B59" s="5" t="s">
-        <v>107</v>
-      </c>
-      <c r="C59" s="5">
-        <v>15</v>
-      </c>
-      <c r="D59" s="6">
-        <v>127000</v>
-      </c>
-      <c r="E59" s="6">
-        <v>144000</v>
-      </c>
-      <c r="F59" s="6">
-        <v>17000</v>
-      </c>
-      <c r="G59" s="6">
-        <f t="shared" si="2"/>
-        <v>17000</v>
-      </c>
-      <c r="H59" s="6">
-        <f t="shared" si="3"/>
-        <v>144000</v>
-      </c>
-      <c r="I59" s="5" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="60" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A60" s="5" t="s">
-        <v>120</v>
-      </c>
-      <c r="B60" s="5" t="s">
-        <v>107</v>
-      </c>
-      <c r="C60" s="5">
-        <v>16</v>
-      </c>
-      <c r="D60" s="6">
-        <v>139000</v>
-      </c>
-      <c r="E60" s="6">
-        <v>151000</v>
-      </c>
-      <c r="F60" s="6">
-        <v>12000</v>
-      </c>
-      <c r="G60" s="6">
-        <f t="shared" si="2"/>
-        <v>12000</v>
-      </c>
-      <c r="H60" s="6">
-        <f t="shared" si="3"/>
-        <v>151000</v>
-      </c>
-      <c r="I60" s="5" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="61" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A61" s="5" t="s">
-        <v>121</v>
-      </c>
-      <c r="B61" s="5" t="s">
-        <v>107</v>
-      </c>
-      <c r="C61" s="5">
-        <v>16</v>
-      </c>
-      <c r="D61" s="6">
-        <v>150000</v>
-      </c>
-      <c r="E61" s="6">
-        <v>151000</v>
-      </c>
-      <c r="F61" s="6">
-        <v>1000</v>
-      </c>
-      <c r="G61" s="6">
-        <f t="shared" si="2"/>
-        <v>1000</v>
-      </c>
-      <c r="H61" s="6">
-        <f t="shared" si="3"/>
-        <v>151000</v>
-      </c>
-      <c r="I61" s="5" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="62" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A62" s="5" t="s">
-        <v>125</v>
-      </c>
-      <c r="B62" s="5" t="s">
-        <v>123</v>
-      </c>
-      <c r="C62" s="5">
-        <v>13</v>
-      </c>
-      <c r="D62" s="6">
-        <v>106000</v>
-      </c>
-      <c r="E62" s="6">
-        <v>115000</v>
-      </c>
-      <c r="F62" s="6">
-        <v>9000</v>
-      </c>
-      <c r="G62" s="6">
-        <f t="shared" si="2"/>
-        <v>9000</v>
-      </c>
-      <c r="H62" s="6">
-        <f t="shared" si="3"/>
-        <v>115000</v>
-      </c>
-      <c r="I62" s="5" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="63" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A63" s="5" t="s">
-        <v>127</v>
-      </c>
-      <c r="B63" s="5" t="s">
-        <v>123</v>
-      </c>
-      <c r="C63" s="5">
-        <v>13</v>
-      </c>
-      <c r="D63" s="6">
-        <v>110000</v>
-      </c>
-      <c r="E63" s="6">
-        <v>115000</v>
-      </c>
-      <c r="F63" s="6">
-        <v>5000</v>
-      </c>
-      <c r="G63" s="6">
-        <f t="shared" si="2"/>
-        <v>5000</v>
-      </c>
-      <c r="H63" s="6">
-        <f t="shared" si="3"/>
-        <v>115000</v>
-      </c>
-      <c r="I63" s="5" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="64" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A64" s="5" t="s">
-        <v>50</v>
-      </c>
-      <c r="B64" s="5" t="s">
-        <v>123</v>
-      </c>
-      <c r="C64" s="5">
-        <v>14</v>
-      </c>
-      <c r="D64" s="6">
-        <v>115000</v>
-      </c>
-      <c r="E64" s="6">
-        <v>122000</v>
-      </c>
-      <c r="F64" s="6">
-        <v>7000</v>
-      </c>
-      <c r="G64" s="6">
-        <f t="shared" si="2"/>
-        <v>7000</v>
-      </c>
-      <c r="H64" s="6">
-        <f t="shared" si="3"/>
-        <v>122000</v>
-      </c>
-      <c r="I64" s="5" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="65" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A65" s="5" t="s">
-        <v>128</v>
-      </c>
-      <c r="B65" s="5" t="s">
-        <v>123</v>
-      </c>
-      <c r="C65" s="5">
-        <v>14</v>
-      </c>
-      <c r="D65" s="6">
-        <v>121000</v>
-      </c>
-      <c r="E65" s="6">
-        <v>122000</v>
-      </c>
-      <c r="F65" s="6">
-        <v>1000</v>
-      </c>
-      <c r="G65" s="6">
-        <f t="shared" si="2"/>
-        <v>1000</v>
-      </c>
-      <c r="H65" s="6">
-        <f t="shared" si="3"/>
-        <v>122000</v>
-      </c>
-      <c r="I65" s="5" t="s">
-        <v>171</v>
-      </c>
+      <c r="D22" s="9">
+        <v>0</v>
+      </c>
+      <c r="E22" s="4" t="s">
+        <v>178</v>
+      </c>
+      <c r="F22" s="6"/>
+      <c r="G22" s="12"/>
+      <c r="H22" s="15"/>
+      <c r="I22" s="16"/>
+      <c r="J22" s="15"/>
+      <c r="K22" s="15"/>
+      <c r="L22" s="12"/>
+      <c r="M22" s="12"/>
+      <c r="N22" s="12"/>
+      <c r="O22" s="12"/>
+    </row>
+    <row r="23" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="D23">
+        <f>SUM(D13:D22)</f>
+        <v>100000</v>
+      </c>
+      <c r="E23" s="6"/>
+      <c r="F23" s="6"/>
+      <c r="G23" s="13"/>
+      <c r="H23" s="13"/>
+      <c r="I23" s="12"/>
+      <c r="J23" s="12"/>
+      <c r="K23" s="12"/>
+      <c r="L23" s="12"/>
+      <c r="M23" s="12"/>
+      <c r="N23" s="12"/>
+      <c r="O23" s="12"/>
+    </row>
+    <row r="24" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="D24" s="6"/>
+      <c r="E24" s="6"/>
+      <c r="F24" s="6"/>
+      <c r="G24" s="13"/>
+      <c r="H24" s="13"/>
+      <c r="I24" s="12"/>
+      <c r="J24" s="12"/>
+      <c r="K24" s="12"/>
+      <c r="L24" s="12"/>
+      <c r="M24" s="12"/>
+      <c r="N24" s="12"/>
+      <c r="O24" s="12"/>
+    </row>
+    <row r="25" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A25" t="s">
+        <v>180</v>
+      </c>
+      <c r="D25" s="6"/>
+      <c r="E25" s="6"/>
+      <c r="F25" s="6"/>
+      <c r="G25" s="13"/>
+      <c r="H25" s="13"/>
+      <c r="I25" s="12"/>
+      <c r="J25" s="12"/>
+      <c r="K25" s="12"/>
+      <c r="L25" s="12"/>
+      <c r="M25" s="12"/>
+      <c r="N25" s="12"/>
+      <c r="O25" s="12"/>
+    </row>
+    <row r="26" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="D26" s="6"/>
+      <c r="E26" s="6"/>
+      <c r="F26" s="6"/>
+      <c r="G26" s="13"/>
+      <c r="H26" s="13"/>
+      <c r="I26" s="12"/>
+      <c r="J26" s="12"/>
+      <c r="K26" s="12"/>
+      <c r="L26" s="12"/>
+      <c r="M26" s="12"/>
+      <c r="N26" s="12"/>
+      <c r="O26" s="12"/>
+    </row>
+    <row r="27" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="D27" s="6"/>
+      <c r="E27" s="6"/>
+      <c r="F27" s="6"/>
+      <c r="G27" s="13"/>
+      <c r="H27" s="13"/>
+      <c r="I27" s="12"/>
+      <c r="J27" s="12"/>
+      <c r="K27" s="12"/>
+      <c r="L27" s="12"/>
+      <c r="M27" s="12"/>
+      <c r="N27" s="12"/>
+      <c r="O27" s="12"/>
+    </row>
+    <row r="28" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="D28" s="6"/>
+      <c r="E28" s="6"/>
+      <c r="F28" s="6"/>
+      <c r="G28" s="6"/>
+      <c r="H28" s="6"/>
+    </row>
+    <row r="29" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="D29" s="6"/>
+      <c r="E29" s="6"/>
+      <c r="F29" s="6"/>
+      <c r="G29" s="6"/>
+      <c r="H29" s="6"/>
+    </row>
+    <row r="30" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="D30" s="6"/>
+      <c r="E30" s="6"/>
+      <c r="F30" s="6"/>
+      <c r="G30" s="6"/>
+      <c r="H30" s="6"/>
+    </row>
+    <row r="31" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="D31" s="6"/>
+      <c r="E31" s="6"/>
+      <c r="F31" s="6"/>
+      <c r="G31" s="6"/>
+      <c r="H31" s="6"/>
+    </row>
+    <row r="32" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="D32" s="6"/>
+      <c r="E32" s="6"/>
+      <c r="F32" s="6"/>
+      <c r="G32" s="6"/>
+      <c r="H32" s="6"/>
+    </row>
+    <row r="33" spans="4:8" x14ac:dyDescent="0.2">
+      <c r="D33" s="6"/>
+      <c r="E33" s="6"/>
+      <c r="F33" s="6"/>
+      <c r="G33" s="6"/>
+      <c r="H33" s="6"/>
+    </row>
+    <row r="34" spans="4:8" x14ac:dyDescent="0.2">
+      <c r="D34" s="6"/>
+      <c r="E34" s="6"/>
+      <c r="F34" s="6"/>
+      <c r="G34" s="6"/>
+      <c r="H34" s="6"/>
+    </row>
+    <row r="35" spans="4:8" x14ac:dyDescent="0.2">
+      <c r="D35" s="6"/>
+      <c r="E35" s="6"/>
+      <c r="F35" s="6"/>
+      <c r="G35" s="6"/>
+      <c r="H35" s="6"/>
+    </row>
+    <row r="36" spans="4:8" x14ac:dyDescent="0.2">
+      <c r="D36" s="6"/>
+      <c r="E36" s="6"/>
+      <c r="F36" s="6"/>
+      <c r="G36" s="6"/>
+      <c r="H36" s="6"/>
+    </row>
+    <row r="37" spans="4:8" x14ac:dyDescent="0.2">
+      <c r="D37" s="6"/>
+      <c r="E37" s="6"/>
+      <c r="F37" s="6"/>
+      <c r="G37" s="6"/>
+      <c r="H37" s="6"/>
+    </row>
+    <row r="38" spans="4:8" x14ac:dyDescent="0.2">
+      <c r="D38" s="6"/>
+      <c r="E38" s="6"/>
+      <c r="F38" s="6"/>
+      <c r="G38" s="6"/>
+      <c r="H38" s="6"/>
+    </row>
+    <row r="39" spans="4:8" x14ac:dyDescent="0.2">
+      <c r="D39" s="6"/>
+      <c r="E39" s="6"/>
+      <c r="F39" s="6"/>
+      <c r="G39" s="6"/>
+      <c r="H39" s="6"/>
+    </row>
+    <row r="40" spans="4:8" x14ac:dyDescent="0.2">
+      <c r="D40" s="6"/>
+      <c r="E40" s="6"/>
+      <c r="F40" s="6"/>
+      <c r="G40" s="6"/>
+      <c r="H40" s="6"/>
+    </row>
+    <row r="41" spans="4:8" x14ac:dyDescent="0.2">
+      <c r="D41" s="6"/>
+      <c r="E41" s="6"/>
+      <c r="F41" s="6"/>
+      <c r="G41" s="6"/>
+      <c r="H41" s="6"/>
+    </row>
+    <row r="42" spans="4:8" x14ac:dyDescent="0.2">
+      <c r="D42" s="6"/>
+      <c r="E42" s="6"/>
+      <c r="F42" s="6"/>
+      <c r="G42" s="6"/>
+      <c r="H42" s="6"/>
+    </row>
+    <row r="43" spans="4:8" x14ac:dyDescent="0.2">
+      <c r="D43" s="6"/>
+      <c r="E43" s="6"/>
+      <c r="F43" s="6"/>
+      <c r="G43" s="6"/>
+      <c r="H43" s="6"/>
+    </row>
+    <row r="44" spans="4:8" x14ac:dyDescent="0.2">
+      <c r="D44" s="6"/>
+      <c r="E44" s="6"/>
+      <c r="F44" s="6"/>
+      <c r="G44" s="6"/>
+      <c r="H44" s="6"/>
+    </row>
+    <row r="45" spans="4:8" x14ac:dyDescent="0.2">
+      <c r="D45" s="6"/>
+      <c r="E45" s="6"/>
+      <c r="F45" s="6"/>
+      <c r="G45" s="6"/>
+      <c r="H45" s="6"/>
+    </row>
+    <row r="46" spans="4:8" x14ac:dyDescent="0.2">
+      <c r="D46" s="6"/>
+      <c r="E46" s="6"/>
+      <c r="F46" s="6"/>
+      <c r="G46" s="6"/>
+      <c r="H46" s="6"/>
+    </row>
+    <row r="47" spans="4:8" x14ac:dyDescent="0.2">
+      <c r="D47" s="6"/>
+      <c r="E47" s="6"/>
+      <c r="F47" s="6"/>
+      <c r="G47" s="6"/>
+      <c r="H47" s="6"/>
+    </row>
+    <row r="48" spans="4:8" x14ac:dyDescent="0.2">
+      <c r="D48" s="6"/>
+      <c r="E48" s="6"/>
+      <c r="F48" s="6"/>
+      <c r="G48" s="6"/>
+      <c r="H48" s="6"/>
+    </row>
+    <row r="49" spans="4:8" x14ac:dyDescent="0.2">
+      <c r="D49" s="6"/>
+      <c r="E49" s="6"/>
+      <c r="F49" s="6"/>
+      <c r="G49" s="6"/>
+      <c r="H49" s="6"/>
+    </row>
+    <row r="50" spans="4:8" x14ac:dyDescent="0.2">
+      <c r="D50" s="6"/>
+      <c r="E50" s="6"/>
+      <c r="F50" s="6"/>
+      <c r="G50" s="6"/>
+      <c r="H50" s="6"/>
+    </row>
+    <row r="51" spans="4:8" x14ac:dyDescent="0.2">
+      <c r="D51" s="6"/>
+      <c r="E51" s="6"/>
+      <c r="F51" s="6"/>
+      <c r="G51" s="6"/>
+      <c r="H51" s="6"/>
+    </row>
+    <row r="52" spans="4:8" x14ac:dyDescent="0.2">
+      <c r="D52" s="6"/>
+      <c r="E52" s="6"/>
+      <c r="F52" s="6"/>
+      <c r="G52" s="6"/>
+      <c r="H52" s="6"/>
+    </row>
+    <row r="53" spans="4:8" x14ac:dyDescent="0.2">
+      <c r="D53" s="6"/>
+      <c r="E53" s="6"/>
+      <c r="F53" s="6"/>
+      <c r="G53" s="6"/>
+      <c r="H53" s="6"/>
+    </row>
+    <row r="54" spans="4:8" x14ac:dyDescent="0.2">
+      <c r="D54" s="6"/>
+      <c r="E54" s="6"/>
+      <c r="F54" s="6"/>
+      <c r="G54" s="6"/>
+      <c r="H54" s="6"/>
+    </row>
+    <row r="55" spans="4:8" x14ac:dyDescent="0.2">
+      <c r="D55" s="6"/>
+      <c r="E55" s="6"/>
+      <c r="F55" s="6"/>
+      <c r="G55" s="6"/>
+      <c r="H55" s="6"/>
+    </row>
+    <row r="56" spans="4:8" x14ac:dyDescent="0.2">
+      <c r="D56" s="6"/>
+      <c r="E56" s="6"/>
+      <c r="F56" s="6"/>
+      <c r="G56" s="6"/>
+      <c r="H56" s="6"/>
+    </row>
+    <row r="57" spans="4:8" x14ac:dyDescent="0.2">
+      <c r="D57" s="6"/>
+      <c r="E57" s="6"/>
+      <c r="F57" s="6"/>
+      <c r="G57" s="6"/>
+      <c r="H57" s="6"/>
+    </row>
+    <row r="58" spans="4:8" x14ac:dyDescent="0.2">
+      <c r="D58" s="6"/>
+      <c r="E58" s="6"/>
+      <c r="F58" s="6"/>
+      <c r="G58" s="6"/>
+      <c r="H58" s="6"/>
+    </row>
+    <row r="59" spans="4:8" x14ac:dyDescent="0.2">
+      <c r="D59" s="6"/>
+      <c r="E59" s="6"/>
+      <c r="F59" s="6"/>
+      <c r="G59" s="6"/>
+      <c r="H59" s="6"/>
+    </row>
+    <row r="60" spans="4:8" x14ac:dyDescent="0.2">
+      <c r="D60" s="6"/>
+      <c r="E60" s="6"/>
+      <c r="F60" s="6"/>
+      <c r="G60" s="6"/>
+      <c r="H60" s="6"/>
+    </row>
+    <row r="61" spans="4:8" x14ac:dyDescent="0.2">
+      <c r="D61" s="6"/>
+      <c r="E61" s="6"/>
+      <c r="F61" s="6"/>
+      <c r="G61" s="6"/>
+      <c r="H61" s="6"/>
+    </row>
+    <row r="62" spans="4:8" x14ac:dyDescent="0.2">
+      <c r="D62" s="6"/>
+      <c r="E62" s="6"/>
+      <c r="F62" s="6"/>
+      <c r="G62" s="6"/>
+      <c r="H62" s="6"/>
+    </row>
+    <row r="63" spans="4:8" x14ac:dyDescent="0.2">
+      <c r="D63" s="6"/>
+      <c r="E63" s="6"/>
+      <c r="F63" s="6"/>
+      <c r="G63" s="6"/>
+      <c r="H63" s="6"/>
+    </row>
+    <row r="64" spans="4:8" x14ac:dyDescent="0.2">
+      <c r="D64" s="6"/>
+      <c r="E64" s="6"/>
+      <c r="F64" s="6"/>
+      <c r="G64" s="6"/>
+      <c r="H64" s="6"/>
+    </row>
+    <row r="65" spans="4:8" x14ac:dyDescent="0.2">
+      <c r="D65" s="6"/>
+      <c r="E65" s="6"/>
+      <c r="F65" s="6"/>
+      <c r="G65" s="6"/>
+      <c r="H65" s="6"/>
     </row>
   </sheetData>
+  <conditionalFormatting sqref="A12:E22 A25">
+    <cfRule type="containsText" dxfId="7" priority="5" operator="containsText" text="Перенос">
+      <formula>NOT(ISERROR(SEARCH("Перенос",A12)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="6" priority="6" operator="containsText" text="Частично">
+      <formula>NOT(ISERROR(SEARCH("Частично",A12)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A12:E23 A25">
+    <cfRule type="containsText" dxfId="5" priority="7" operator="containsText" text="Частнично">
+      <formula>NOT(ISERROR(SEARCH("Частнично",A12)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="4" priority="8" operator="containsText" text="Поднят">
+      <formula>NOT(ISERROR(SEARCH("Поднят",A12)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G12:K22">
+    <cfRule type="containsText" dxfId="3" priority="1" operator="containsText" text="Перенос">
+      <formula>NOT(ISERROR(SEARCH("Перенос",G12)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="2" priority="2" operator="containsText" text="Частично">
+      <formula>NOT(ISERROR(SEARCH("Частично",G12)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G12:K22">
+    <cfRule type="containsText" dxfId="1" priority="3" operator="containsText" text="Частнично">
+      <formula>NOT(ISERROR(SEARCH("Частнично",G12)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="0" priority="4" operator="containsText" text="Поднят">
+      <formula>NOT(ISERROR(SEARCH("Поднят",G12)))</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7EA843C8-ACCF-004B-BA41-941B2E49A80F}">
-  <dimension ref="A1"/>
+  <dimension ref="A1:B6"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
-  <sheetData/>
+  <cols>
+    <col min="1" max="1" width="16.1640625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
+        <v>173</v>
+      </c>
+      <c r="B1" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>182</v>
+      </c>
+      <c r="B2">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>183</v>
+      </c>
+      <c r="B3">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>184</v>
+      </c>
+      <c r="B4">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>185</v>
+      </c>
+      <c r="B5">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
+        <v>186</v>
+      </c>
+      <c r="B6">
+        <v>3</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </worksheet>
